--- a/03_Outputs/Agroindustrial_Occidente/06_Desarrollo_Rural/desarrollo_rural.xlsx
+++ b/03_Outputs/Agroindustrial_Occidente/06_Desarrollo_Rural/desarrollo_rural.xlsx
@@ -81,7 +81,7 @@
     <numFmt numFmtId="218" formatCode="#,##0.00"/>
     <numFmt numFmtId="219" formatCode="#,##0.00"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -91,23 +91,162 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos Narrow"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -127,7 +266,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0"/>
     <xf applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0"/>
@@ -148,9 +287,13 @@
     <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="178" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="179" xfId="0"/>
     <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="180" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="181" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="182" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="183" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="184" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="185" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="186" xfId="0"/>
@@ -158,35 +301,56 @@
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="188" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="189" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="190" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="5" fontId="5" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="191" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="192" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="192" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="6" fontId="7" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="193" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="194" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="195" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="7" fontId="8" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="196" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="197" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="9" numFmtId="197" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="198" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="199" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="9" numFmtId="199" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="200" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="201" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="9" numFmtId="201" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="202" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="203" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="9" numFmtId="203" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="204" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="205" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="9" numFmtId="205" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="206" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="207" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="9" numFmtId="207" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="208" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="209" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="9" numFmtId="209" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="210" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="211" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="9" numFmtId="211" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="8" fontId="10" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="212" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="213" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="11" numFmtId="213" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="214" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="215" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="11" numFmtId="215" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="216" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="217" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="11" numFmtId="217" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="218" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="219" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="11" numFmtId="219" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="9" fontId="12" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="10" fontId="13" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="11" fontId="14" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="12" fontId="15" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="13" fontId="16" numFmtId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -515,17 +679,17 @@
   <dimension ref="A1:L64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="44.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="6" max="7" bestFit="1" customWidth="1" hidden="false" width="7.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="6.711"/>
-    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="7.711"/>
-    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
-    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="45.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+    <col min="6" max="7" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="7.711"/>
+    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
+    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -627,11 +791,15 @@
       <c r="J2" s="14">
         <v>715</v>
       </c>
-      <c r="K2" s="16">
-        <v>0</v>
-      </c>
-      <c r="L2" s="18">
-        <v>10089</v>
+      <c r="K2" s="16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L2" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -671,11 +839,15 @@
       <c r="J3" s="14">
         <v>1325</v>
       </c>
-      <c r="K3" s="16">
-        <v>0</v>
-      </c>
-      <c r="L3" s="18">
-        <v>17711</v>
+      <c r="K3" s="16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L3" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -715,11 +887,15 @@
       <c r="J4" s="14">
         <v>2284</v>
       </c>
-      <c r="K4" s="16">
-        <v>0</v>
-      </c>
-      <c r="L4" s="18">
-        <v>32774</v>
+      <c r="K4" s="16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L4" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -759,11 +935,15 @@
       <c r="J5" s="14">
         <v>1981</v>
       </c>
-      <c r="K5" s="16">
-        <v>0</v>
-      </c>
-      <c r="L5" s="18">
-        <v>30492</v>
+      <c r="K5" s="16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L5" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -803,11 +983,15 @@
       <c r="J6" s="14">
         <v>2400</v>
       </c>
-      <c r="K6" s="16">
-        <v>0</v>
-      </c>
-      <c r="L6" s="18">
-        <v>8551</v>
+      <c r="K6" s="16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L6" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -847,11 +1031,15 @@
       <c r="J7" s="14">
         <v>1303</v>
       </c>
-      <c r="K7" s="16">
-        <v>0</v>
-      </c>
-      <c r="L7" s="18">
-        <v>12607</v>
+      <c r="K7" s="16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L7" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -897,7 +1085,7 @@
         <v>0</v>
       </c>
       <c r="L8" s="19">
-        <v>112224</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -943,7 +1131,7 @@
         <v>56553</v>
       </c>
       <c r="L9" s="19">
-        <v>282228</v>
+        <v>73934</v>
       </c>
     </row>
     <row r="10">
@@ -989,7 +1177,7 @@
         <v>606143</v>
       </c>
       <c r="L10" s="19">
-        <v>4007472</v>
+        <v>1101682</v>
       </c>
     </row>
     <row r="11">
@@ -3416,29 +3604,29 @@
   <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="79" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="79" t="inlineStr">
         <is>
           <t>ciclo</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="79" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="79" t="inlineStr">
         <is>
           <t>serie</t>
         </is>
@@ -3696,40 +3884,40 @@
   <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="3" max="4" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+    <col min="3" max="4" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="81" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="81" t="inlineStr">
         <is>
           <t>anio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="81" t="inlineStr">
         <is>
           <t>prod_perm</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="81" t="inlineStr">
         <is>
           <t>prod_tran</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="81" t="inlineStr">
         <is>
           <t>prod_total</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="81" t="inlineStr">
         <is>
           <t>pct_prod_prov</t>
         </is>
@@ -3879,35 +4067,35 @@
   <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="83" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="83" t="inlineStr">
         <is>
           <t>anio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="83" t="inlineStr">
         <is>
           <t>produccion_cultivo</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="83" t="inlineStr">
         <is>
           <t>area_cosechada</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="83" t="inlineStr">
         <is>
           <t>rendimiento</t>
         </is>
@@ -4039,46 +4227,46 @@
   <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
+    <col min="1" max="2" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="21" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="21" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="21" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="21" t="inlineStr">
         <is>
           <t>Año</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="21" t="inlineStr">
         <is>
           <t>Total especies pecuarias</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="21" t="inlineStr">
         <is>
           <t>Participación en el total provincial (%)</t>
         </is>
@@ -4103,14 +4291,18 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E2" s="20">
+      <c r="E2" s="22">
         <v>2019</v>
       </c>
-      <c r="F2" s="21">
-        <v>10089</v>
-      </c>
-      <c r="G2" s="22">
-        <v>0.0899005560307956</v>
+      <c r="F2" s="23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G2" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -4132,14 +4324,18 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E3" s="20">
+      <c r="E3" s="22">
         <v>2019</v>
       </c>
-      <c r="F3" s="21">
-        <v>17711</v>
-      </c>
-      <c r="G3" s="22">
-        <v>0.157818291987454</v>
+      <c r="F3" s="23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G3" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -4161,14 +4357,18 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E4" s="20">
+      <c r="E4" s="22">
         <v>2019</v>
       </c>
-      <c r="F4" s="21">
-        <v>32774</v>
-      </c>
-      <c r="G4" s="22">
-        <v>0.292040918163673</v>
+      <c r="F4" s="23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G4" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -4190,14 +4390,18 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E5" s="20">
+      <c r="E5" s="22">
         <v>2019</v>
       </c>
-      <c r="F5" s="21">
-        <v>30492</v>
-      </c>
-      <c r="G5" s="22">
-        <v>0.271706586826347</v>
+      <c r="F5" s="23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -4219,14 +4423,18 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="22">
         <v>2019</v>
       </c>
-      <c r="F6" s="21">
-        <v>8551</v>
-      </c>
-      <c r="G6" s="22">
-        <v>0.0761958226404334</v>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -4248,14 +4456,18 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="22">
         <v>2019</v>
       </c>
-      <c r="F7" s="21">
-        <v>12607</v>
-      </c>
-      <c r="G7" s="22">
-        <v>0.112337824351297</v>
+      <c r="F7" s="23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -4277,13 +4489,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="22">
         <v>2020</v>
       </c>
-      <c r="F8" s="21">
+      <c r="F8" s="23">
         <v>10381</v>
       </c>
-      <c r="G8" s="22">
+      <c r="G8" s="24">
         <v>0.0843476282561711</v>
       </c>
     </row>
@@ -4306,13 +4518,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E9" s="20">
+      <c r="E9" s="22">
         <v>2020</v>
       </c>
-      <c r="F9" s="21">
+      <c r="F9" s="23">
         <v>21981</v>
       </c>
-      <c r="G9" s="22">
+      <c r="G9" s="24">
         <v>0.178599866746835</v>
       </c>
     </row>
@@ -4335,13 +4547,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E10" s="20">
+      <c r="E10" s="22">
         <v>2020</v>
       </c>
-      <c r="F10" s="21">
+      <c r="F10" s="23">
         <v>32845</v>
       </c>
-      <c r="G10" s="22">
+      <c r="G10" s="24">
         <v>0.266871963209126</v>
       </c>
     </row>
@@ -4364,13 +4576,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E11" s="20">
+      <c r="E11" s="22">
         <v>2020</v>
       </c>
-      <c r="F11" s="21">
+      <c r="F11" s="23">
         <v>35038</v>
       </c>
-      <c r="G11" s="22">
+      <c r="G11" s="24">
         <v>0.284690511399646</v>
       </c>
     </row>
@@ -4393,13 +4605,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E12" s="20">
+      <c r="E12" s="22">
         <v>2020</v>
       </c>
-      <c r="F12" s="21">
+      <c r="F12" s="23">
         <v>9178</v>
       </c>
-      <c r="G12" s="22">
+      <c r="G12" s="24">
         <v>0.0745730211092513</v>
       </c>
     </row>
@@ -4422,13 +4634,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E13" s="20">
+      <c r="E13" s="22">
         <v>2020</v>
       </c>
-      <c r="F13" s="21">
+      <c r="F13" s="23">
         <v>13651</v>
       </c>
-      <c r="G13" s="22">
+      <c r="G13" s="24">
         <v>0.11091700927897</v>
       </c>
     </row>
@@ -4451,13 +4663,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E14" s="20">
+      <c r="E14" s="22">
         <v>2021</v>
       </c>
-      <c r="F14" s="21">
+      <c r="F14" s="23">
         <v>10083</v>
       </c>
-      <c r="G14" s="22">
+      <c r="G14" s="24">
         <v>0.0828342575477511</v>
       </c>
     </row>
@@ -4480,13 +4692,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E15" s="20">
+      <c r="E15" s="22">
         <v>2021</v>
       </c>
-      <c r="F15" s="21">
+      <c r="F15" s="23">
         <v>22065</v>
       </c>
-      <c r="G15" s="22">
+      <c r="G15" s="24">
         <v>0.181269254467036</v>
       </c>
     </row>
@@ -4509,13 +4721,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E16" s="20">
+      <c r="E16" s="22">
         <v>2021</v>
       </c>
-      <c r="F16" s="21">
+      <c r="F16" s="23">
         <v>33363</v>
       </c>
-      <c r="G16" s="22">
+      <c r="G16" s="24">
         <v>0.274085027726433</v>
       </c>
     </row>
@@ -4538,13 +4750,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E17" s="20">
+      <c r="E17" s="22">
         <v>2021</v>
       </c>
-      <c r="F17" s="21">
+      <c r="F17" s="23">
         <v>33612</v>
       </c>
-      <c r="G17" s="22">
+      <c r="G17" s="24">
         <v>0.276130622304375</v>
       </c>
     </row>
@@ -4567,13 +4779,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E18" s="20">
+      <c r="E18" s="22">
         <v>2021</v>
       </c>
-      <c r="F18" s="21">
+      <c r="F18" s="23">
         <v>9521</v>
       </c>
-      <c r="G18" s="22">
+      <c r="G18" s="24">
         <v>0.0782172930786609</v>
       </c>
     </row>
@@ -4596,13 +4808,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E19" s="20">
+      <c r="E19" s="22">
         <v>2021</v>
       </c>
-      <c r="F19" s="21">
+      <c r="F19" s="23">
         <v>13081</v>
       </c>
-      <c r="G19" s="22">
+      <c r="G19" s="24">
         <v>0.107463544875745</v>
       </c>
     </row>
@@ -4625,13 +4837,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E20" s="20">
+      <c r="E20" s="22">
         <v>2022</v>
       </c>
-      <c r="F20" s="21">
+      <c r="F20" s="23">
         <v>13510</v>
       </c>
-      <c r="G20" s="22">
+      <c r="G20" s="24">
         <v>0.103800911235239</v>
       </c>
     </row>
@@ -4654,13 +4866,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E21" s="20">
+      <c r="E21" s="22">
         <v>2022</v>
       </c>
-      <c r="F21" s="21">
+      <c r="F21" s="23">
         <v>20808</v>
       </c>
-      <c r="G21" s="22">
+      <c r="G21" s="24">
         <v>0.159873379791476</v>
       </c>
     </row>
@@ -4683,13 +4895,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E22" s="20">
+      <c r="E22" s="22">
         <v>2022</v>
       </c>
-      <c r="F22" s="21">
+      <c r="F22" s="23">
         <v>34246</v>
       </c>
-      <c r="G22" s="22">
+      <c r="G22" s="24">
         <v>0.263121095940931</v>
       </c>
     </row>
@@ -4712,13 +4924,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E23" s="20">
+      <c r="E23" s="22">
         <v>2022</v>
       </c>
-      <c r="F23" s="21">
+      <c r="F23" s="23">
         <v>39605</v>
       </c>
-      <c r="G23" s="22">
+      <c r="G23" s="24">
         <v>0.304295713506412</v>
       </c>
     </row>
@@ -4741,13 +4953,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E24" s="20">
+      <c r="E24" s="22">
         <v>2022</v>
       </c>
-      <c r="F24" s="21">
+      <c r="F24" s="23">
         <v>9498</v>
       </c>
-      <c r="G24" s="22">
+      <c r="G24" s="24">
         <v>0.0729756517329604</v>
       </c>
     </row>
@@ -4770,13 +4982,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E25" s="20">
+      <c r="E25" s="22">
         <v>2022</v>
       </c>
-      <c r="F25" s="21">
+      <c r="F25" s="23">
         <v>12486</v>
       </c>
-      <c r="G25" s="22">
+      <c r="G25" s="24">
         <v>0.0959332477929821</v>
       </c>
     </row>
@@ -4799,13 +5011,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E26" s="20">
+      <c r="E26" s="22">
         <v>2023</v>
       </c>
-      <c r="F26" s="21">
+      <c r="F26" s="23">
         <v>12116</v>
       </c>
-      <c r="G26" s="22">
+      <c r="G26" s="24">
         <v>0.0941187437369398</v>
       </c>
     </row>
@@ -4828,13 +5040,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E27" s="20">
+      <c r="E27" s="22">
         <v>2023</v>
       </c>
-      <c r="F27" s="21">
+      <c r="F27" s="23">
         <v>19592</v>
       </c>
-      <c r="G27" s="22">
+      <c r="G27" s="24">
         <v>0.152193333385121</v>
       </c>
     </row>
@@ -4857,13 +5069,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E28" s="20">
+      <c r="E28" s="22">
         <v>2023</v>
       </c>
-      <c r="F28" s="21">
+      <c r="F28" s="23">
         <v>35406</v>
       </c>
-      <c r="G28" s="22">
+      <c r="G28" s="24">
         <v>0.275038646479869</v>
       </c>
     </row>
@@ -4886,13 +5098,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E29" s="20">
+      <c r="E29" s="22">
         <v>2023</v>
       </c>
-      <c r="F29" s="21">
+      <c r="F29" s="23">
         <v>38895</v>
       </c>
-      <c r="G29" s="22">
+      <c r="G29" s="24">
         <v>0.302141675276351</v>
       </c>
     </row>
@@ -4915,13 +5127,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E30" s="20">
+      <c r="E30" s="22">
         <v>2023</v>
       </c>
-      <c r="F30" s="21">
+      <c r="F30" s="23">
         <v>9898</v>
       </c>
-      <c r="G30" s="22">
+      <c r="G30" s="24">
         <v>0.0768890166315806</v>
       </c>
     </row>
@@ -4944,13 +5156,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E31" s="20">
+      <c r="E31" s="22">
         <v>2023</v>
       </c>
-      <c r="F31" s="21">
+      <c r="F31" s="23">
         <v>12824</v>
       </c>
-      <c r="G31" s="22">
+      <c r="G31" s="24">
         <v>0.0996185844901384</v>
       </c>
     </row>
@@ -4973,13 +5185,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E32" s="20">
+      <c r="E32" s="22">
         <v>2024</v>
       </c>
-      <c r="F32" s="21">
+      <c r="F32" s="23">
         <v>12755</v>
       </c>
-      <c r="G32" s="22">
+      <c r="G32" s="24">
         <v>0.0973835100819228</v>
       </c>
     </row>
@@ -5002,13 +5214,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E33" s="20">
+      <c r="E33" s="22">
         <v>2024</v>
       </c>
-      <c r="F33" s="21">
+      <c r="F33" s="23">
         <v>21104</v>
       </c>
-      <c r="G33" s="22">
+      <c r="G33" s="24">
         <v>0.161127526206891</v>
       </c>
     </row>
@@ -5031,13 +5243,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E34" s="20">
+      <c r="E34" s="22">
         <v>2024</v>
       </c>
-      <c r="F34" s="21">
+      <c r="F34" s="23">
         <v>34950</v>
       </c>
-      <c r="G34" s="22">
+      <c r="G34" s="24">
         <v>0.266840743031219</v>
       </c>
     </row>
@@ -5060,13 +5272,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E35" s="20">
+      <c r="E35" s="22">
         <v>2024</v>
       </c>
-      <c r="F35" s="21">
+      <c r="F35" s="23">
         <v>39060</v>
       </c>
-      <c r="G35" s="22">
+      <c r="G35" s="24">
         <v>0.298220298220298</v>
       </c>
     </row>
@@ -5089,13 +5301,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E36" s="20">
+      <c r="E36" s="22">
         <v>2024</v>
       </c>
-      <c r="F36" s="21">
+      <c r="F36" s="23">
         <v>10556</v>
       </c>
-      <c r="G36" s="22">
+      <c r="G36" s="24">
         <v>0.080594302816525</v>
       </c>
     </row>
@@ -5118,13 +5330,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E37" s="20">
+      <c r="E37" s="22">
         <v>2024</v>
       </c>
-      <c r="F37" s="21">
+      <c r="F37" s="23">
         <v>12552</v>
       </c>
-      <c r="G37" s="22">
+      <c r="G37" s="24">
         <v>0.0958336196431435</v>
       </c>
     </row>
@@ -5147,13 +5359,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E38" s="20">
+      <c r="E38" s="22">
         <v>2025</v>
       </c>
-      <c r="F38" s="21">
+      <c r="F38" s="23">
         <v>10141</v>
       </c>
-      <c r="G38" s="22">
+      <c r="G38" s="24">
         <v>0.0806973986806401</v>
       </c>
     </row>
@@ -5176,13 +5388,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E39" s="20">
+      <c r="E39" s="22">
         <v>2025</v>
       </c>
-      <c r="F39" s="21">
+      <c r="F39" s="23">
         <v>20411</v>
       </c>
-      <c r="G39" s="22">
+      <c r="G39" s="24">
         <v>0.162421319837348</v>
       </c>
     </row>
@@ -5205,13 +5417,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E40" s="20">
+      <c r="E40" s="22">
         <v>2025</v>
       </c>
-      <c r="F40" s="21">
+      <c r="F40" s="23">
         <v>34545</v>
       </c>
-      <c r="G40" s="22">
+      <c r="G40" s="24">
         <v>0.274893170044642</v>
       </c>
     </row>
@@ -5234,13 +5446,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E41" s="20">
+      <c r="E41" s="22">
         <v>2025</v>
       </c>
-      <c r="F41" s="21">
+      <c r="F41" s="23">
         <v>38913</v>
       </c>
-      <c r="G41" s="22">
+      <c r="G41" s="24">
         <v>0.309651698536609</v>
       </c>
     </row>
@@ -5263,13 +5475,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E42" s="20">
+      <c r="E42" s="22">
         <v>2025</v>
       </c>
-      <c r="F42" s="21">
+      <c r="F42" s="23">
         <v>9954</v>
       </c>
-      <c r="G42" s="22">
+      <c r="G42" s="24">
         <v>0.0792093389672706</v>
       </c>
     </row>
@@ -5292,13 +5504,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E43" s="20">
+      <c r="E43" s="22">
         <v>2025</v>
       </c>
-      <c r="F43" s="21">
+      <c r="F43" s="23">
         <v>11703</v>
       </c>
-      <c r="G43" s="22">
+      <c r="G43" s="24">
         <v>0.0931270739334909</v>
       </c>
     </row>
@@ -5314,69 +5526,68 @@
   <dimension ref="A1:K43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="7" max="8" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
-    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="1" max="2" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="7" max="9" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
+    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="26" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="26" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="26" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="26" t="inlineStr">
         <is>
           <t>Año</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="26" t="inlineStr">
         <is>
           <t>Bovinos (%)</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="26" t="inlineStr">
         <is>
           <t>Búfalos (%)</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="26" t="inlineStr">
         <is>
           <t>Caprinos (%)</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="26" t="inlineStr">
         <is>
           <t>Ovinos (%)</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="26" t="inlineStr">
         <is>
           <t>Equinos (%)</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="26" t="inlineStr">
         <is>
           <t>Porcinos (%)</t>
         </is>
@@ -5401,26 +5612,38 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E2" s="23">
+      <c r="E2" s="27">
         <v>2019</v>
       </c>
-      <c r="F2" s="24">
-        <v>0.927247497274259</v>
-      </c>
-      <c r="G2" s="25">
-        <v>0</v>
-      </c>
-      <c r="H2" s="26">
-        <v>0.000594707106749926</v>
-      </c>
-      <c r="I2" s="27">
-        <v>0.00128853206462484</v>
-      </c>
-      <c r="J2" s="28">
-        <v>0.0708692635543661</v>
-      </c>
-      <c r="K2" s="29">
-        <v>0</v>
+      <c r="F2" s="28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G2" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H2" s="30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I2" s="31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J2" s="32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K2" s="33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -5442,26 +5665,38 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E3" s="23">
+      <c r="E3" s="27">
         <v>2019</v>
       </c>
-      <c r="F3" s="24">
-        <v>0.920840155835357</v>
-      </c>
-      <c r="G3" s="25">
-        <v>0</v>
-      </c>
-      <c r="H3" s="26">
-        <v>0.00299249054260064</v>
-      </c>
-      <c r="I3" s="27">
-        <v>0.00135509005702671</v>
-      </c>
-      <c r="J3" s="28">
-        <v>0.0748122635650161</v>
-      </c>
-      <c r="K3" s="29">
-        <v>0</v>
+      <c r="F3" s="28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G3" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H3" s="30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I3" s="31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J3" s="32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K3" s="33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -5483,26 +5718,38 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E4" s="23">
+      <c r="E4" s="27">
         <v>2019</v>
       </c>
-      <c r="F4" s="24">
-        <v>0.92463538170501</v>
-      </c>
-      <c r="G4" s="25">
-        <v>0</v>
-      </c>
-      <c r="H4" s="26">
-        <v>0.000335631903338012</v>
-      </c>
-      <c r="I4" s="27">
-        <v>0.00533959846219564</v>
-      </c>
-      <c r="J4" s="28">
-        <v>0.0696893879294563</v>
-      </c>
-      <c r="K4" s="29">
-        <v>0</v>
+      <c r="F4" s="28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G4" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H4" s="30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I4" s="31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J4" s="32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K4" s="33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -5524,26 +5771,38 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E5" s="23">
+      <c r="E5" s="27">
         <v>2019</v>
       </c>
-      <c r="F5" s="24">
-        <v>0.928046700773974</v>
-      </c>
-      <c r="G5" s="25">
-        <v>0.00301718483536665</v>
-      </c>
-      <c r="H5" s="26">
-        <v>0.00298438934802571</v>
-      </c>
-      <c r="I5" s="27">
-        <v>0.000983864620228257</v>
-      </c>
-      <c r="J5" s="28">
-        <v>0.0649678604224059</v>
-      </c>
-      <c r="K5" s="29">
-        <v>0</v>
+      <c r="F5" s="28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H5" s="30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I5" s="31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J5" s="32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K5" s="33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -5565,26 +5824,38 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E6" s="23">
+      <c r="E6" s="27">
         <v>2019</v>
       </c>
-      <c r="F6" s="24">
-        <v>0.718161618524149</v>
-      </c>
-      <c r="G6" s="25">
-        <v>0</v>
-      </c>
-      <c r="H6" s="26">
-        <v>0.000116945386504502</v>
-      </c>
-      <c r="I6" s="27">
-        <v>0.00105250847854052</v>
-      </c>
-      <c r="J6" s="28">
-        <v>0.280668927610806</v>
-      </c>
-      <c r="K6" s="29">
-        <v>0</v>
+      <c r="F6" s="28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H6" s="30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I6" s="31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J6" s="32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K6" s="33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -5606,26 +5877,38 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="27">
         <v>2019</v>
       </c>
-      <c r="F7" s="24">
-        <v>0.89505830094392</v>
-      </c>
-      <c r="G7" s="25">
-        <v>0</v>
-      </c>
-      <c r="H7" s="26">
-        <v>0.0000793210121361149</v>
-      </c>
-      <c r="I7" s="27">
-        <v>0.00150709923058618</v>
-      </c>
-      <c r="J7" s="28">
-        <v>0.103355278813358</v>
-      </c>
-      <c r="K7" s="29">
-        <v>0</v>
+      <c r="F7" s="28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H7" s="30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I7" s="31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J7" s="32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K7" s="33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -5647,25 +5930,25 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="27">
         <v>2020</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="28">
         <v>0.884211540314035</v>
       </c>
-      <c r="G8" s="25">
+      <c r="G8" s="29">
         <v>0</v>
       </c>
-      <c r="H8" s="26">
+      <c r="H8" s="30">
         <v>0.000674308833445718</v>
       </c>
-      <c r="I8" s="27">
+      <c r="I8" s="31">
         <v>0.00115595800019266</v>
       </c>
-      <c r="J8" s="28">
+      <c r="J8" s="32">
         <v>0.0701281186783547</v>
       </c>
-      <c r="K8" s="29">
+      <c r="K8" s="33">
         <v>0.0438300741739717</v>
       </c>
     </row>
@@ -5688,25 +5971,25 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E9" s="23">
+      <c r="E9" s="27">
         <v>2020</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="28">
         <v>0.760201992629999</v>
       </c>
-      <c r="G9" s="25">
+      <c r="G9" s="29">
         <v>0.000227469177926391</v>
       </c>
-      <c r="H9" s="26">
+      <c r="H9" s="30">
         <v>0.00591419862608617</v>
       </c>
-      <c r="I9" s="27">
+      <c r="I9" s="31">
         <v>0.0010463582184614</v>
       </c>
-      <c r="J9" s="28">
+      <c r="J9" s="32">
         <v>0.067694827350894</v>
       </c>
-      <c r="K9" s="29">
+      <c r="K9" s="33">
         <v>0.164915153996633</v>
       </c>
     </row>
@@ -5729,25 +6012,25 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E10" s="23">
+      <c r="E10" s="27">
         <v>2020</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="28">
         <v>0.909940630232912</v>
       </c>
-      <c r="G10" s="25">
+      <c r="G10" s="29">
         <v>0.000152230172020094</v>
       </c>
-      <c r="H10" s="26">
+      <c r="H10" s="30">
         <v>0</v>
       </c>
-      <c r="I10" s="27">
+      <c r="I10" s="31">
         <v>0.00517582584868321</v>
       </c>
-      <c r="J10" s="28">
+      <c r="J10" s="32">
         <v>0.0717308570558685</v>
       </c>
-      <c r="K10" s="29">
+      <c r="K10" s="33">
         <v>0.0130004566905161</v>
       </c>
     </row>
@@ -5770,25 +6053,25 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E11" s="23">
+      <c r="E11" s="27">
         <v>2020</v>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="28">
         <v>0.8265597351447</v>
       </c>
-      <c r="G11" s="25">
+      <c r="G11" s="29">
         <v>0.00199783092642274</v>
       </c>
-      <c r="H11" s="26">
+      <c r="H11" s="30">
         <v>0.00259718020434956</v>
       </c>
-      <c r="I11" s="27">
+      <c r="I11" s="31">
         <v>0.000713511045150979</v>
       </c>
-      <c r="J11" s="28">
+      <c r="J11" s="32">
         <v>0.0606769792796392</v>
       </c>
-      <c r="K11" s="29">
+      <c r="K11" s="33">
         <v>0.107454763399737</v>
       </c>
     </row>
@@ -5811,25 +6094,25 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E12" s="23">
+      <c r="E12" s="27">
         <v>2020</v>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="28">
         <v>0.711810852037481</v>
       </c>
-      <c r="G12" s="25">
+      <c r="G12" s="29">
         <v>0</v>
       </c>
-      <c r="H12" s="26">
+      <c r="H12" s="30">
         <v>0.000108956199607758</v>
       </c>
-      <c r="I12" s="27">
+      <c r="I12" s="31">
         <v>0.000980605796469819</v>
       </c>
-      <c r="J12" s="28">
+      <c r="J12" s="32">
         <v>0.268903900631946</v>
       </c>
-      <c r="K12" s="29">
+      <c r="K12" s="33">
         <v>0.0181956853344955</v>
       </c>
     </row>
@@ -5852,25 +6135,25 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E13" s="23">
+      <c r="E13" s="27">
         <v>2020</v>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="28">
         <v>0.863526481576441</v>
       </c>
-      <c r="G13" s="25">
+      <c r="G13" s="29">
         <v>0.0003662735330745</v>
       </c>
-      <c r="H13" s="26">
+      <c r="H13" s="30">
         <v>0.0000732547066149</v>
       </c>
-      <c r="I13" s="27">
+      <c r="I13" s="31">
         <v>0.0013918394256831</v>
       </c>
-      <c r="J13" s="28">
+      <c r="J13" s="32">
         <v>0.10270309867409</v>
       </c>
-      <c r="K13" s="29">
+      <c r="K13" s="33">
         <v>0.0319390520840964</v>
       </c>
     </row>
@@ -5893,25 +6176,25 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E14" s="23">
+      <c r="E14" s="27">
         <v>2021</v>
       </c>
-      <c r="F14" s="24">
+      <c r="F14" s="28">
         <v>0.902509173856987</v>
       </c>
-      <c r="G14" s="25">
+      <c r="G14" s="29">
         <v>0</v>
       </c>
-      <c r="H14" s="26">
+      <c r="H14" s="30">
         <v>0.0000991768322919766</v>
       </c>
-      <c r="I14" s="27">
+      <c r="I14" s="31">
         <v>0</v>
       </c>
-      <c r="J14" s="28">
+      <c r="J14" s="32">
         <v>0.0709114350887633</v>
       </c>
-      <c r="K14" s="29">
+      <c r="K14" s="33">
         <v>0.0264802142219577</v>
       </c>
     </row>
@@ -5934,25 +6217,25 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E15" s="23">
+      <c r="E15" s="27">
         <v>2021</v>
       </c>
-      <c r="F15" s="24">
+      <c r="F15" s="28">
         <v>0.724631769771131</v>
       </c>
-      <c r="G15" s="25">
+      <c r="G15" s="29">
         <v>0.000181282574212554</v>
       </c>
-      <c r="H15" s="26">
+      <c r="H15" s="30">
         <v>0.000453206435531385</v>
       </c>
-      <c r="I15" s="27">
+      <c r="I15" s="31">
         <v>0.000317244504871969</v>
       </c>
-      <c r="J15" s="28">
+      <c r="J15" s="32">
         <v>0.188080670745525</v>
       </c>
-      <c r="K15" s="29">
+      <c r="K15" s="33">
         <v>0.0863358259687288</v>
       </c>
     </row>
@@ -5975,25 +6258,25 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E16" s="23">
+      <c r="E16" s="27">
         <v>2021</v>
       </c>
-      <c r="F16" s="24">
+      <c r="F16" s="28">
         <v>0.912867547882385</v>
       </c>
-      <c r="G16" s="25">
+      <c r="G16" s="29">
         <v>0</v>
       </c>
-      <c r="H16" s="26">
+      <c r="H16" s="30">
         <v>0.00506549171237599</v>
       </c>
-      <c r="I16" s="27">
+      <c r="I16" s="31">
         <v>0.00293738572670323</v>
       </c>
-      <c r="J16" s="28">
+      <c r="J16" s="32">
         <v>0.0706171507358451</v>
       </c>
-      <c r="K16" s="29">
+      <c r="K16" s="33">
         <v>0.008512423942691</v>
       </c>
     </row>
@@ -6016,25 +6299,25 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E17" s="23">
+      <c r="E17" s="27">
         <v>2021</v>
       </c>
-      <c r="F17" s="24">
+      <c r="F17" s="28">
         <v>0.867011781506605</v>
       </c>
-      <c r="G17" s="25">
+      <c r="G17" s="29">
         <v>0.00214209210996073</v>
       </c>
-      <c r="H17" s="26">
+      <c r="H17" s="30">
         <v>0.000416517910270142</v>
       </c>
-      <c r="I17" s="27">
+      <c r="I17" s="31">
         <v>0.0011900511722004</v>
       </c>
-      <c r="J17" s="28">
+      <c r="J17" s="32">
         <v>0.0632512198024515</v>
       </c>
-      <c r="K17" s="29">
+      <c r="K17" s="33">
         <v>0.0659883374985124</v>
       </c>
     </row>
@@ -6057,25 +6340,25 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E18" s="23">
+      <c r="E18" s="27">
         <v>2021</v>
       </c>
-      <c r="F18" s="24">
+      <c r="F18" s="28">
         <v>0.693519588278542</v>
       </c>
-      <c r="G18" s="25">
+      <c r="G18" s="29">
         <v>0</v>
       </c>
-      <c r="H18" s="26">
+      <c r="H18" s="30">
         <v>0</v>
       </c>
-      <c r="I18" s="27">
+      <c r="I18" s="31">
         <v>0</v>
       </c>
-      <c r="J18" s="28">
+      <c r="J18" s="32">
         <v>0.259216468858313</v>
       </c>
-      <c r="K18" s="29">
+      <c r="K18" s="33">
         <v>0.0472639428631446</v>
       </c>
     </row>
@@ -6098,25 +6381,25 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E19" s="23">
+      <c r="E19" s="27">
         <v>2021</v>
       </c>
-      <c r="F19" s="24">
+      <c r="F19" s="28">
         <v>0.858726397064445</v>
       </c>
-      <c r="G19" s="25">
+      <c r="G19" s="29">
         <v>0.000535127283846801</v>
       </c>
-      <c r="H19" s="26">
+      <c r="H19" s="30">
         <v>0</v>
       </c>
-      <c r="I19" s="27">
+      <c r="I19" s="31">
         <v>0.00229340264505772</v>
       </c>
-      <c r="J19" s="28">
+      <c r="J19" s="32">
         <v>0.107178350279031</v>
       </c>
-      <c r="K19" s="29">
+      <c r="K19" s="33">
         <v>0.0312667227276202</v>
       </c>
     </row>
@@ -6139,25 +6422,25 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E20" s="23">
+      <c r="E20" s="27">
         <v>2022</v>
       </c>
-      <c r="F20" s="24">
+      <c r="F20" s="28">
         <v>0.71621021465581</v>
       </c>
-      <c r="G20" s="25">
+      <c r="G20" s="29">
         <v>0</v>
       </c>
-      <c r="H20" s="26">
+      <c r="H20" s="30">
         <v>0.00155440414507772</v>
       </c>
-      <c r="I20" s="27">
+      <c r="I20" s="31">
         <v>0.00540340488527017</v>
       </c>
-      <c r="J20" s="28">
+      <c r="J20" s="32">
         <v>0.266987416728349</v>
       </c>
-      <c r="K20" s="29">
+      <c r="K20" s="33">
         <v>0.00984455958549223</v>
       </c>
     </row>
@@ -6180,25 +6463,25 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E21" s="23">
+      <c r="E21" s="27">
         <v>2022</v>
       </c>
-      <c r="F21" s="24">
+      <c r="F21" s="28">
         <v>0.781958861976163</v>
       </c>
-      <c r="G21" s="25">
+      <c r="G21" s="29">
         <v>0.000192233756247597</v>
       </c>
-      <c r="H21" s="26">
+      <c r="H21" s="30">
         <v>0.000480584390618993</v>
       </c>
-      <c r="I21" s="27">
+      <c r="I21" s="31">
         <v>0.000480584390618993</v>
       </c>
-      <c r="J21" s="28">
+      <c r="J21" s="32">
         <v>0.0768454440599769</v>
       </c>
-      <c r="K21" s="29">
+      <c r="K21" s="33">
         <v>0.140042291426374</v>
       </c>
     </row>
@@ -6221,25 +6504,25 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E22" s="23">
+      <c r="E22" s="27">
         <v>2022</v>
       </c>
-      <c r="F22" s="24">
+      <c r="F22" s="28">
         <v>0.908456462068563</v>
       </c>
-      <c r="G22" s="25">
+      <c r="G22" s="29">
         <v>0.000146002452841208</v>
       </c>
-      <c r="H22" s="26">
+      <c r="H22" s="30">
         <v>0.00181043041523098</v>
       </c>
-      <c r="I22" s="27">
+      <c r="I22" s="31">
         <v>0.0115341937744554</v>
       </c>
-      <c r="J22" s="28">
+      <c r="J22" s="32">
         <v>0.0653214974011563</v>
       </c>
-      <c r="K22" s="29">
+      <c r="K22" s="33">
         <v>0.0127314138877533</v>
       </c>
     </row>
@@ -6262,25 +6545,25 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E23" s="23">
+      <c r="E23" s="27">
         <v>2022</v>
       </c>
-      <c r="F23" s="24">
+      <c r="F23" s="28">
         <v>0.761318015402096</v>
       </c>
-      <c r="G23" s="25">
+      <c r="G23" s="29">
         <v>0.00234818836005555</v>
       </c>
-      <c r="H23" s="26">
+      <c r="H23" s="30">
         <v>0.000959474813786138</v>
       </c>
-      <c r="I23" s="27">
+      <c r="I23" s="31">
         <v>0.00186845095316248</v>
       </c>
-      <c r="J23" s="28">
+      <c r="J23" s="32">
         <v>0.0554727938391617</v>
       </c>
-      <c r="K23" s="29">
+      <c r="K23" s="33">
         <v>0.178033076631738</v>
       </c>
     </row>
@@ -6303,25 +6586,25 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E24" s="23">
+      <c r="E24" s="27">
         <v>2022</v>
       </c>
-      <c r="F24" s="24">
+      <c r="F24" s="28">
         <v>0.707517372078332</v>
       </c>
-      <c r="G24" s="25">
+      <c r="G24" s="29">
         <v>0</v>
       </c>
-      <c r="H24" s="26">
+      <c r="H24" s="30">
         <v>0.00210570646451885</v>
       </c>
-      <c r="I24" s="27">
+      <c r="I24" s="31">
         <v>0.00294798905032638</v>
       </c>
-      <c r="J24" s="28">
+      <c r="J24" s="32">
         <v>0.0768582859549379</v>
       </c>
-      <c r="K24" s="29">
+      <c r="K24" s="33">
         <v>0.210570646451885</v>
       </c>
     </row>
@@ -6344,25 +6627,25 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E25" s="23">
+      <c r="E25" s="27">
         <v>2022</v>
       </c>
-      <c r="F25" s="24">
+      <c r="F25" s="28">
         <v>0.891238186769181</v>
       </c>
-      <c r="G25" s="25">
+      <c r="G25" s="29">
         <v>0.000480538202787122</v>
       </c>
-      <c r="H25" s="26">
+      <c r="H25" s="30">
         <v>0</v>
       </c>
-      <c r="I25" s="27">
+      <c r="I25" s="31">
         <v>0.00264296011532917</v>
       </c>
-      <c r="J25" s="28">
+      <c r="J25" s="32">
         <v>0.0937049495434887</v>
       </c>
-      <c r="K25" s="29">
+      <c r="K25" s="33">
         <v>0.0119333653692135</v>
       </c>
     </row>
@@ -6385,25 +6668,25 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E26" s="23">
+      <c r="E26" s="27">
         <v>2023</v>
       </c>
-      <c r="F26" s="24">
+      <c r="F26" s="28">
         <v>0.763535820402773</v>
       </c>
-      <c r="G26" s="25">
+      <c r="G26" s="29">
         <v>0</v>
       </c>
-      <c r="H26" s="26">
+      <c r="H26" s="30">
         <v>0</v>
       </c>
-      <c r="I26" s="27">
+      <c r="I26" s="31">
         <v>0</v>
       </c>
-      <c r="J26" s="28">
+      <c r="J26" s="32">
         <v>0.225486959392539</v>
       </c>
-      <c r="K26" s="29">
+      <c r="K26" s="33">
         <v>0.010977220204688</v>
       </c>
     </row>
@@ -6426,25 +6709,25 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E27" s="23">
+      <c r="E27" s="27">
         <v>2023</v>
       </c>
-      <c r="F27" s="24">
+      <c r="F27" s="28">
         <v>0.806706819109841</v>
       </c>
-      <c r="G27" s="25">
+      <c r="G27" s="29">
         <v>0.000204164965291956</v>
       </c>
-      <c r="H27" s="26">
+      <c r="H27" s="30">
         <v>0</v>
       </c>
-      <c r="I27" s="27">
+      <c r="I27" s="31">
         <v>0.000153123723968967</v>
       </c>
-      <c r="J27" s="28">
+      <c r="J27" s="32">
         <v>0.0442017149857085</v>
       </c>
-      <c r="K27" s="29">
+      <c r="K27" s="33">
         <v>0.14873417721519</v>
       </c>
     </row>
@@ -6467,25 +6750,25 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E28" s="23">
+      <c r="E28" s="27">
         <v>2023</v>
       </c>
-      <c r="F28" s="24">
+      <c r="F28" s="28">
         <v>0.891798000338926</v>
       </c>
-      <c r="G28" s="25">
+      <c r="G28" s="29">
         <v>0.00107326441846015</v>
       </c>
-      <c r="H28" s="26">
+      <c r="H28" s="30">
         <v>0.000141219002428967</v>
       </c>
-      <c r="I28" s="27">
+      <c r="I28" s="31">
         <v>0</v>
       </c>
-      <c r="J28" s="28">
+      <c r="J28" s="32">
         <v>0.0946732192283794</v>
       </c>
-      <c r="K28" s="29">
+      <c r="K28" s="33">
         <v>0.0123142970118059</v>
       </c>
     </row>
@@ -6508,25 +6791,25 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E29" s="23">
+      <c r="E29" s="27">
         <v>2023</v>
       </c>
-      <c r="F29" s="24">
+      <c r="F29" s="28">
         <v>0.755007070317522</v>
       </c>
-      <c r="G29" s="25">
+      <c r="G29" s="29">
         <v>0.00362514462013112</v>
       </c>
-      <c r="H29" s="26">
+      <c r="H29" s="30">
         <v>0.0000771307365985345</v>
       </c>
-      <c r="I29" s="27">
+      <c r="I29" s="31">
         <v>0.000462784419591207</v>
       </c>
-      <c r="J29" s="28">
+      <c r="J29" s="32">
         <v>0.0595449286540686</v>
       </c>
-      <c r="K29" s="29">
+      <c r="K29" s="33">
         <v>0.181282941252089</v>
       </c>
     </row>
@@ -6549,25 +6832,25 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E30" s="23">
+      <c r="E30" s="27">
         <v>2023</v>
       </c>
-      <c r="F30" s="24">
+      <c r="F30" s="28">
         <v>0.727419680743585</v>
       </c>
-      <c r="G30" s="25">
+      <c r="G30" s="29">
         <v>0</v>
       </c>
-      <c r="H30" s="26">
+      <c r="H30" s="30">
         <v>0</v>
       </c>
-      <c r="I30" s="27">
+      <c r="I30" s="31">
         <v>0</v>
       </c>
-      <c r="J30" s="28">
+      <c r="J30" s="32">
         <v>0.070519296827642</v>
       </c>
-      <c r="K30" s="29">
+      <c r="K30" s="33">
         <v>0.202061022428773</v>
       </c>
     </row>
@@ -6590,25 +6873,25 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E31" s="23">
+      <c r="E31" s="27">
         <v>2023</v>
       </c>
-      <c r="F31" s="24">
+      <c r="F31" s="28">
         <v>0.900031191515908</v>
       </c>
-      <c r="G31" s="25">
+      <c r="G31" s="29">
         <v>0.000623830318153462</v>
       </c>
-      <c r="H31" s="26">
+      <c r="H31" s="30">
         <v>0</v>
       </c>
-      <c r="I31" s="27">
+      <c r="I31" s="31">
         <v>0.00148159700561447</v>
       </c>
-      <c r="J31" s="28">
+      <c r="J31" s="32">
         <v>0.0862445414847162</v>
       </c>
-      <c r="K31" s="29">
+      <c r="K31" s="33">
         <v>0.0116188396756082</v>
       </c>
     </row>
@@ -6631,25 +6914,25 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E32" s="23">
+      <c r="E32" s="27">
         <v>2024</v>
       </c>
-      <c r="F32" s="24">
+      <c r="F32" s="28">
         <v>0.704116032928263</v>
       </c>
-      <c r="G32" s="25">
+      <c r="G32" s="29">
         <v>0</v>
       </c>
-      <c r="H32" s="26">
+      <c r="H32" s="30">
         <v>0.00172481379851039</v>
       </c>
-      <c r="I32" s="27">
+      <c r="I32" s="31">
         <v>0</v>
       </c>
-      <c r="J32" s="28">
+      <c r="J32" s="32">
         <v>0.282791062328499</v>
       </c>
-      <c r="K32" s="29">
+      <c r="K32" s="33">
         <v>0.0113680909447276</v>
       </c>
     </row>
@@ -6672,25 +6955,25 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E33" s="23">
+      <c r="E33" s="27">
         <v>2024</v>
       </c>
-      <c r="F33" s="24">
+      <c r="F33" s="28">
         <v>0.776961713419257</v>
       </c>
-      <c r="G33" s="25">
+      <c r="G33" s="29">
         <v>0.0000947687642153146</v>
       </c>
-      <c r="H33" s="26">
+      <c r="H33" s="30">
         <v>0.000473843821076573</v>
       </c>
-      <c r="I33" s="27">
+      <c r="I33" s="31">
         <v>0.000142153146322972</v>
       </c>
-      <c r="J33" s="28">
+      <c r="J33" s="32">
         <v>0.0736827141774071</v>
       </c>
-      <c r="K33" s="29">
+      <c r="K33" s="33">
         <v>0.148644806671721</v>
       </c>
     </row>
@@ -6713,25 +6996,25 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E34" s="23">
+      <c r="E34" s="27">
         <v>2024</v>
       </c>
-      <c r="F34" s="24">
+      <c r="F34" s="28">
         <v>0.905979971387697</v>
       </c>
-      <c r="G34" s="25">
+      <c r="G34" s="29">
         <v>0.000944206008583691</v>
       </c>
-      <c r="H34" s="26">
+      <c r="H34" s="30">
         <v>0.000858369098712446</v>
       </c>
-      <c r="I34" s="27">
+      <c r="I34" s="31">
         <v>0</v>
       </c>
-      <c r="J34" s="28">
+      <c r="J34" s="32">
         <v>0.076824034334764</v>
       </c>
-      <c r="K34" s="29">
+      <c r="K34" s="33">
         <v>0.0153934191702432</v>
       </c>
     </row>
@@ -6754,25 +7037,25 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E35" s="23">
+      <c r="E35" s="27">
         <v>2024</v>
       </c>
-      <c r="F35" s="24">
+      <c r="F35" s="28">
         <v>0.756554019457245</v>
       </c>
-      <c r="G35" s="25">
+      <c r="G35" s="29">
         <v>0.0025857654889913</v>
       </c>
-      <c r="H35" s="26">
+      <c r="H35" s="30">
         <v>0.000256016385048643</v>
       </c>
-      <c r="I35" s="27">
+      <c r="I35" s="31">
         <v>0.000460829493087558</v>
       </c>
-      <c r="J35" s="28">
+      <c r="J35" s="32">
         <v>0.0539938556067588</v>
       </c>
-      <c r="K35" s="29">
+      <c r="K35" s="33">
         <v>0.186149513568868</v>
       </c>
     </row>
@@ -6795,25 +7078,25 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E36" s="23">
+      <c r="E36" s="27">
         <v>2024</v>
       </c>
-      <c r="F36" s="24">
+      <c r="F36" s="28">
         <v>0.730295566502463</v>
       </c>
-      <c r="G36" s="25">
+      <c r="G36" s="29">
         <v>0</v>
       </c>
-      <c r="H36" s="26">
+      <c r="H36" s="30">
         <v>0.00189465706707086</v>
       </c>
-      <c r="I36" s="27">
+      <c r="I36" s="31">
         <v>0</v>
       </c>
-      <c r="J36" s="28">
+      <c r="J36" s="32">
         <v>0.0686813186813187</v>
       </c>
-      <c r="K36" s="29">
+      <c r="K36" s="33">
         <v>0.199128457749147</v>
       </c>
     </row>
@@ -6836,25 +7119,25 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E37" s="23">
+      <c r="E37" s="27">
         <v>2024</v>
       </c>
-      <c r="F37" s="24">
+      <c r="F37" s="28">
         <v>0.892527087316762</v>
       </c>
-      <c r="G37" s="25">
+      <c r="G37" s="29">
         <v>0.00127469725940089</v>
       </c>
-      <c r="H37" s="26">
+      <c r="H37" s="30">
         <v>0</v>
       </c>
-      <c r="I37" s="27">
+      <c r="I37" s="31">
         <v>0.00151370299553856</v>
       </c>
-      <c r="J37" s="28">
+      <c r="J37" s="32">
         <v>0.0928138942001275</v>
       </c>
-      <c r="K37" s="29">
+      <c r="K37" s="33">
         <v>0.0118706182281708</v>
       </c>
     </row>
@@ -6877,25 +7160,25 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E38" s="23">
+      <c r="E38" s="27">
         <v>2025</v>
       </c>
-      <c r="F38" s="24">
+      <c r="F38" s="28">
         <v>0.943989744601124</v>
       </c>
-      <c r="G38" s="25">
+      <c r="G38" s="29">
         <v>0</v>
       </c>
-      <c r="H38" s="26">
+      <c r="H38" s="30">
         <v>0.00197219209150971</v>
       </c>
-      <c r="I38" s="27">
+      <c r="I38" s="31">
         <v>0</v>
       </c>
-      <c r="J38" s="28">
+      <c r="J38" s="32">
         <v>0.0397396706439207</v>
       </c>
-      <c r="K38" s="29">
+      <c r="K38" s="33">
         <v>0.0142983926634454</v>
       </c>
     </row>
@@ -6918,25 +7201,25 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E39" s="23">
+      <c r="E39" s="27">
         <v>2025</v>
       </c>
-      <c r="F39" s="24">
+      <c r="F39" s="28">
         <v>0.798491009749645</v>
       </c>
-      <c r="G39" s="25">
+      <c r="G39" s="29">
         <v>0.0000979863798931948</v>
       </c>
-      <c r="H39" s="26">
+      <c r="H39" s="30">
         <v>0.000342952329626182</v>
       </c>
-      <c r="I39" s="27">
+      <c r="I39" s="31">
         <v>0.000734897849198961</v>
       </c>
-      <c r="J39" s="28">
+      <c r="J39" s="32">
         <v>0.0466415168291607</v>
       </c>
-      <c r="K39" s="29">
+      <c r="K39" s="33">
         <v>0.153691636862476</v>
       </c>
     </row>
@@ -6959,25 +7242,25 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E40" s="23">
+      <c r="E40" s="27">
         <v>2025</v>
       </c>
-      <c r="F40" s="24">
+      <c r="F40" s="28">
         <v>0.930293819655522</v>
       </c>
-      <c r="G40" s="25">
+      <c r="G40" s="29">
         <v>0.000984223476624692</v>
       </c>
-      <c r="H40" s="26">
+      <c r="H40" s="30">
         <v>0.000752641482124765</v>
       </c>
-      <c r="I40" s="27">
+      <c r="I40" s="31">
         <v>0</v>
       </c>
-      <c r="J40" s="28">
+      <c r="J40" s="32">
         <v>0.0523954262556086</v>
       </c>
-      <c r="K40" s="29">
+      <c r="K40" s="33">
         <v>0.0155738891301201</v>
       </c>
     </row>
@@ -7000,25 +7283,25 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E41" s="23">
+      <c r="E41" s="27">
         <v>2025</v>
       </c>
-      <c r="F41" s="24">
+      <c r="F41" s="28">
         <v>0.772826561817388</v>
       </c>
-      <c r="G41" s="25">
+      <c r="G41" s="29">
         <v>0.0029810089173284</v>
       </c>
-      <c r="H41" s="26">
+      <c r="H41" s="30">
         <v>0.000205586821884717</v>
       </c>
-      <c r="I41" s="27">
+      <c r="I41" s="31">
         <v>0</v>
       </c>
-      <c r="J41" s="28">
+      <c r="J41" s="32">
         <v>0.037134119702927</v>
       </c>
-      <c r="K41" s="29">
+      <c r="K41" s="33">
         <v>0.186852722740472</v>
       </c>
     </row>
@@ -7041,25 +7324,25 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E42" s="23">
+      <c r="E42" s="27">
         <v>2025</v>
       </c>
-      <c r="F42" s="24">
+      <c r="F42" s="28">
         <v>0.74573035965441</v>
       </c>
-      <c r="G42" s="25">
+      <c r="G42" s="29">
         <v>0</v>
       </c>
-      <c r="H42" s="26">
+      <c r="H42" s="30">
         <v>0.00170785613823588</v>
       </c>
-      <c r="I42" s="27">
+      <c r="I42" s="31">
         <v>0</v>
       </c>
-      <c r="J42" s="28">
+      <c r="J42" s="32">
         <v>0.0413903958207756</v>
       </c>
-      <c r="K42" s="29">
+      <c r="K42" s="33">
         <v>0.211171388386578</v>
       </c>
     </row>
@@ -7082,25 +7365,25 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E43" s="23">
+      <c r="E43" s="27">
         <v>2025</v>
       </c>
-      <c r="F43" s="24">
+      <c r="F43" s="28">
         <v>0.918311544048535</v>
       </c>
-      <c r="G43" s="25">
+      <c r="G43" s="29">
         <v>0.00145261898658464</v>
       </c>
-      <c r="H43" s="26">
+      <c r="H43" s="30">
         <v>0</v>
       </c>
-      <c r="I43" s="27">
+      <c r="I43" s="31">
         <v>0</v>
       </c>
-      <c r="J43" s="28">
+      <c r="J43" s="32">
         <v>0.0675040587883449</v>
       </c>
-      <c r="K43" s="29">
+      <c r="K43" s="33">
         <v>0.0127317781765359</v>
       </c>
     </row>
@@ -7116,35 +7399,35 @@
   <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="44.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="45.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="35" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="35" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="35" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="35" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="35" t="inlineStr">
         <is>
           <t>Área municipal (km²)</t>
         </is>
@@ -7169,7 +7452,7 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E2" s="30">
+      <c r="E2" s="37">
         <v>296.95598</v>
       </c>
     </row>
@@ -7192,7 +7475,7 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E3" s="30">
+      <c r="E3" s="37">
         <v>364.83123</v>
       </c>
     </row>
@@ -7215,7 +7498,7 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E4" s="30">
+      <c r="E4" s="37">
         <v>1957.262708</v>
       </c>
     </row>
@@ -7238,7 +7521,7 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="37">
         <v>1384.131365</v>
       </c>
     </row>
@@ -7261,7 +7544,7 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="37">
         <v>434.069043</v>
       </c>
     </row>
@@ -7284,32 +7567,32 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="37">
         <v>265.930372</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="36" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="36" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="E8" s="31">
+      <c r="D8" s="36" t="inlineStr">
+        <is>
+          <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="E8" s="38">
         <v>4703.180698</v>
       </c>
     </row>
@@ -7325,41 +7608,41 @@
   <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="28.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="43.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="29.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="44.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="29.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="44.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="45.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="40" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="40" t="inlineStr">
         <is>
           <t>Año</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="40" t="inlineStr">
         <is>
           <t>Principal cultivo permanente</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="40" t="inlineStr">
         <is>
           <t>Producción total del cultivo permanente (t)</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="40" t="inlineStr">
         <is>
           <t>Principal cultivo transitorio</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="40" t="inlineStr">
         <is>
           <t>Producción total del cultivo transitorio (t)</t>
         </is>
@@ -7371,7 +7654,7 @@
           <t>Abriaquí</t>
         </is>
       </c>
-      <c r="B2" s="32">
+      <c r="B2" s="41">
         <v>2019</v>
       </c>
       <c r="C2" t="inlineStr">
@@ -7379,7 +7662,7 @@
           <t>Caña</t>
         </is>
       </c>
-      <c r="D2" s="33">
+      <c r="D2" s="42">
         <v>4752</v>
       </c>
       <c r="E2" t="inlineStr">
@@ -7387,7 +7670,7 @@
           <t>Tomate</t>
         </is>
       </c>
-      <c r="F2" s="34">
+      <c r="F2" s="43">
         <v>648</v>
       </c>
     </row>
@@ -7397,7 +7680,7 @@
           <t>Cañasgordas</t>
         </is>
       </c>
-      <c r="B3" s="32">
+      <c r="B3" s="41">
         <v>2019</v>
       </c>
       <c r="C3" t="inlineStr">
@@ -7405,7 +7688,7 @@
           <t>Caña</t>
         </is>
       </c>
-      <c r="D3" s="33">
+      <c r="D3" s="42">
         <v>9732</v>
       </c>
       <c r="E3" t="inlineStr">
@@ -7413,7 +7696,7 @@
           <t>Maíz</t>
         </is>
       </c>
-      <c r="F3" s="34">
+      <c r="F3" s="43">
         <v>302.5</v>
       </c>
     </row>
@@ -7423,7 +7706,7 @@
           <t>Dabeiba</t>
         </is>
       </c>
-      <c r="B4" s="32">
+      <c r="B4" s="41">
         <v>2019</v>
       </c>
       <c r="C4" t="inlineStr">
@@ -7431,7 +7714,7 @@
           <t>Maracuyá</t>
         </is>
       </c>
-      <c r="D4" s="33">
+      <c r="D4" s="42">
         <v>9856</v>
       </c>
       <c r="E4" t="inlineStr">
@@ -7439,7 +7722,7 @@
           <t>Yuca</t>
         </is>
       </c>
-      <c r="F4" s="34">
+      <c r="F4" s="43">
         <v>3700</v>
       </c>
     </row>
@@ -7449,7 +7732,7 @@
           <t>Frontino</t>
         </is>
       </c>
-      <c r="B5" s="32">
+      <c r="B5" s="41">
         <v>2019</v>
       </c>
       <c r="C5" t="inlineStr">
@@ -7457,7 +7740,7 @@
           <t>Caña</t>
         </is>
       </c>
-      <c r="D5" s="33">
+      <c r="D5" s="42">
         <v>12568.92</v>
       </c>
       <c r="E5" t="inlineStr">
@@ -7465,7 +7748,7 @@
           <t>Yuca</t>
         </is>
       </c>
-      <c r="F5" s="34">
+      <c r="F5" s="43">
         <v>196.35</v>
       </c>
     </row>
@@ -7475,7 +7758,7 @@
           <t>Peque</t>
         </is>
       </c>
-      <c r="B6" s="32">
+      <c r="B6" s="41">
         <v>2019</v>
       </c>
       <c r="C6" t="inlineStr">
@@ -7483,7 +7766,7 @@
           <t>Caña</t>
         </is>
       </c>
-      <c r="D6" s="33">
+      <c r="D6" s="42">
         <v>3360</v>
       </c>
       <c r="E6" t="inlineStr">
@@ -7491,7 +7774,7 @@
           <t>Frijol</t>
         </is>
       </c>
-      <c r="F6" s="34">
+      <c r="F6" s="43">
         <v>302</v>
       </c>
     </row>
@@ -7501,7 +7784,7 @@
           <t>Uramita</t>
         </is>
       </c>
-      <c r="B7" s="32">
+      <c r="B7" s="41">
         <v>2019</v>
       </c>
       <c r="C7" t="inlineStr">
@@ -7509,7 +7792,7 @@
           <t>Caña</t>
         </is>
       </c>
-      <c r="D7" s="33">
+      <c r="D7" s="42">
         <v>23560</v>
       </c>
       <c r="E7" t="inlineStr">
@@ -7517,7 +7800,7 @@
           <t>Maíz</t>
         </is>
       </c>
-      <c r="F7" s="34">
+      <c r="F7" s="43">
         <v>3638</v>
       </c>
     </row>
@@ -7527,7 +7810,7 @@
           <t>Abriaquí</t>
         </is>
       </c>
-      <c r="B8" s="32">
+      <c r="B8" s="41">
         <v>2020</v>
       </c>
       <c r="C8" t="inlineStr">
@@ -7535,7 +7818,7 @@
           <t>Caña</t>
         </is>
       </c>
-      <c r="D8" s="33">
+      <c r="D8" s="42">
         <v>5200</v>
       </c>
       <c r="E8" t="inlineStr">
@@ -7543,7 +7826,7 @@
           <t>Tomate</t>
         </is>
       </c>
-      <c r="F8" s="34">
+      <c r="F8" s="43">
         <v>525</v>
       </c>
     </row>
@@ -7553,7 +7836,7 @@
           <t>Cañasgordas</t>
         </is>
       </c>
-      <c r="B9" s="32">
+      <c r="B9" s="41">
         <v>2020</v>
       </c>
       <c r="C9" t="inlineStr">
@@ -7561,7 +7844,7 @@
           <t>Caña</t>
         </is>
       </c>
-      <c r="D9" s="33">
+      <c r="D9" s="42">
         <v>8247.6</v>
       </c>
       <c r="E9" t="inlineStr">
@@ -7569,7 +7852,7 @@
           <t>Maíz</t>
         </is>
       </c>
-      <c r="F9" s="34">
+      <c r="F9" s="43">
         <v>297</v>
       </c>
     </row>
@@ -7579,7 +7862,7 @@
           <t>Dabeiba</t>
         </is>
       </c>
-      <c r="B10" s="32">
+      <c r="B10" s="41">
         <v>2020</v>
       </c>
       <c r="C10" t="inlineStr">
@@ -7587,7 +7870,7 @@
           <t>Caña</t>
         </is>
       </c>
-      <c r="D10" s="33">
+      <c r="D10" s="42">
         <v>8890.5</v>
       </c>
       <c r="E10" t="inlineStr">
@@ -7595,7 +7878,7 @@
           <t>Yuca</t>
         </is>
       </c>
-      <c r="F10" s="34">
+      <c r="F10" s="43">
         <v>6094</v>
       </c>
     </row>
@@ -7605,7 +7888,7 @@
           <t>Frontino</t>
         </is>
       </c>
-      <c r="B11" s="32">
+      <c r="B11" s="41">
         <v>2020</v>
       </c>
       <c r="C11" t="inlineStr">
@@ -7613,7 +7896,7 @@
           <t>Caña</t>
         </is>
       </c>
-      <c r="D11" s="33">
+      <c r="D11" s="42">
         <v>137139.2</v>
       </c>
       <c r="E11" t="inlineStr">
@@ -7621,7 +7904,7 @@
           <t>Yuca</t>
         </is>
       </c>
-      <c r="F11" s="34">
+      <c r="F11" s="43">
         <v>169.4</v>
       </c>
     </row>
@@ -7631,7 +7914,7 @@
           <t>Peque</t>
         </is>
       </c>
-      <c r="B12" s="32">
+      <c r="B12" s="41">
         <v>2020</v>
       </c>
       <c r="C12" t="inlineStr">
@@ -7639,7 +7922,7 @@
           <t>Caña</t>
         </is>
       </c>
-      <c r="D12" s="33">
+      <c r="D12" s="42">
         <v>3040</v>
       </c>
       <c r="E12" t="inlineStr">
@@ -7647,7 +7930,7 @@
           <t>Frijol</t>
         </is>
       </c>
-      <c r="F12" s="34">
+      <c r="F12" s="43">
         <v>353.5</v>
       </c>
     </row>
@@ -7657,7 +7940,7 @@
           <t>Uramita</t>
         </is>
       </c>
-      <c r="B13" s="32">
+      <c r="B13" s="41">
         <v>2020</v>
       </c>
       <c r="C13" t="inlineStr">
@@ -7665,7 +7948,7 @@
           <t>Caña</t>
         </is>
       </c>
-      <c r="D13" s="33">
+      <c r="D13" s="42">
         <v>23960</v>
       </c>
       <c r="E13" t="inlineStr">
@@ -7673,7 +7956,7 @@
           <t>Maíz</t>
         </is>
       </c>
-      <c r="F13" s="34">
+      <c r="F13" s="43">
         <v>5063</v>
       </c>
     </row>
@@ -7683,7 +7966,7 @@
           <t>Abriaquí</t>
         </is>
       </c>
-      <c r="B14" s="32">
+      <c r="B14" s="41">
         <v>2021</v>
       </c>
       <c r="C14" t="inlineStr">
@@ -7691,7 +7974,7 @@
           <t>Caña</t>
         </is>
       </c>
-      <c r="D14" s="33">
+      <c r="D14" s="42">
         <v>5380</v>
       </c>
       <c r="E14" t="inlineStr">
@@ -7699,7 +7982,7 @@
           <t>Tomate</t>
         </is>
       </c>
-      <c r="F14" s="34">
+      <c r="F14" s="43">
         <v>682.5</v>
       </c>
     </row>
@@ -7709,7 +7992,7 @@
           <t>Cañasgordas</t>
         </is>
       </c>
-      <c r="B15" s="32">
+      <c r="B15" s="41">
         <v>2021</v>
       </c>
       <c r="C15" t="inlineStr">
@@ -7717,7 +8000,7 @@
           <t>Caña</t>
         </is>
       </c>
-      <c r="D15" s="33">
+      <c r="D15" s="42">
         <v>8131.6</v>
       </c>
       <c r="E15" t="inlineStr">
@@ -7725,7 +8008,7 @@
           <t>Maíz</t>
         </is>
       </c>
-      <c r="F15" s="34">
+      <c r="F15" s="43">
         <v>328.9</v>
       </c>
     </row>
@@ -7735,7 +8018,7 @@
           <t>Dabeiba</t>
         </is>
       </c>
-      <c r="B16" s="32">
+      <c r="B16" s="41">
         <v>2021</v>
       </c>
       <c r="C16" t="inlineStr">
@@ -7743,7 +8026,7 @@
           <t>Caña</t>
         </is>
       </c>
-      <c r="D16" s="33">
+      <c r="D16" s="42">
         <v>9050.79</v>
       </c>
       <c r="E16" t="inlineStr">
@@ -7751,7 +8034,7 @@
           <t>Yuca</t>
         </is>
       </c>
-      <c r="F16" s="34">
+      <c r="F16" s="43">
         <v>4410</v>
       </c>
     </row>
@@ -7761,7 +8044,7 @@
           <t>Frontino</t>
         </is>
       </c>
-      <c r="B17" s="32">
+      <c r="B17" s="41">
         <v>2021</v>
       </c>
       <c r="C17" t="inlineStr">
@@ -7769,7 +8052,7 @@
           <t>Caña</t>
         </is>
       </c>
-      <c r="D17" s="33">
+      <c r="D17" s="42">
         <v>81600</v>
       </c>
       <c r="E17" t="inlineStr">
@@ -7777,7 +8060,7 @@
           <t>Yuca</t>
         </is>
       </c>
-      <c r="F17" s="34">
+      <c r="F17" s="43">
         <v>168</v>
       </c>
     </row>
@@ -7787,7 +8070,7 @@
           <t>Peque</t>
         </is>
       </c>
-      <c r="B18" s="32">
+      <c r="B18" s="41">
         <v>2021</v>
       </c>
       <c r="C18" t="inlineStr">
@@ -7795,7 +8078,7 @@
           <t>Caña</t>
         </is>
       </c>
-      <c r="D18" s="33">
+      <c r="D18" s="42">
         <v>3080</v>
       </c>
       <c r="E18" t="inlineStr">
@@ -7803,7 +8086,7 @@
           <t>Frijol</t>
         </is>
       </c>
-      <c r="F18" s="34">
+      <c r="F18" s="43">
         <v>283</v>
       </c>
     </row>
@@ -7813,7 +8096,7 @@
           <t>Uramita</t>
         </is>
       </c>
-      <c r="B19" s="32">
+      <c r="B19" s="41">
         <v>2021</v>
       </c>
       <c r="C19" t="inlineStr">
@@ -7821,7 +8104,7 @@
           <t>Caña</t>
         </is>
       </c>
-      <c r="D19" s="33">
+      <c r="D19" s="42">
         <v>28485</v>
       </c>
       <c r="E19" t="inlineStr">
@@ -7829,7 +8112,7 @@
           <t>Ahuyama</t>
         </is>
       </c>
-      <c r="F19" s="34">
+      <c r="F19" s="43">
         <v>3850</v>
       </c>
     </row>
@@ -7839,7 +8122,7 @@
           <t>Abriaquí</t>
         </is>
       </c>
-      <c r="B20" s="32">
+      <c r="B20" s="41">
         <v>2022</v>
       </c>
       <c r="C20" t="inlineStr">
@@ -7847,7 +8130,7 @@
           <t>Caña</t>
         </is>
       </c>
-      <c r="D20" s="33">
+      <c r="D20" s="42">
         <v>5180</v>
       </c>
       <c r="E20" t="inlineStr">
@@ -7855,7 +8138,7 @@
           <t>Tomate</t>
         </is>
       </c>
-      <c r="F20" s="34">
+      <c r="F20" s="43">
         <v>1995</v>
       </c>
     </row>
@@ -7865,7 +8148,7 @@
           <t>Cañasgordas</t>
         </is>
       </c>
-      <c r="B21" s="32">
+      <c r="B21" s="41">
         <v>2022</v>
       </c>
       <c r="C21" t="inlineStr">
@@ -7873,7 +8156,7 @@
           <t>Caña</t>
         </is>
       </c>
-      <c r="D21" s="33">
+      <c r="D21" s="42">
         <v>7203.6</v>
       </c>
       <c r="E21" t="inlineStr">
@@ -7881,7 +8164,7 @@
           <t>Maíz</t>
         </is>
       </c>
-      <c r="F21" s="34">
+      <c r="F21" s="43">
         <v>271.6</v>
       </c>
     </row>
@@ -7891,7 +8174,7 @@
           <t>Dabeiba</t>
         </is>
       </c>
-      <c r="B22" s="32">
+      <c r="B22" s="41">
         <v>2022</v>
       </c>
       <c r="C22" t="inlineStr">
@@ -7899,7 +8182,7 @@
           <t>Caña</t>
         </is>
       </c>
-      <c r="D22" s="33">
+      <c r="D22" s="42">
         <v>5159.5</v>
       </c>
       <c r="E22" t="inlineStr">
@@ -7907,7 +8190,7 @@
           <t>Yuca</t>
         </is>
       </c>
-      <c r="F22" s="34">
+      <c r="F22" s="43">
         <v>4420</v>
       </c>
     </row>
@@ -7917,7 +8200,7 @@
           <t>Frontino</t>
         </is>
       </c>
-      <c r="B23" s="32">
+      <c r="B23" s="41">
         <v>2022</v>
       </c>
       <c r="C23" t="inlineStr">
@@ -7925,7 +8208,7 @@
           <t>Caña</t>
         </is>
       </c>
-      <c r="D23" s="33">
+      <c r="D23" s="42">
         <v>106719.6</v>
       </c>
       <c r="E23" t="inlineStr">
@@ -7933,7 +8216,7 @@
           <t>Yuca</t>
         </is>
       </c>
-      <c r="F23" s="34">
+      <c r="F23" s="43">
         <v>140.25</v>
       </c>
     </row>
@@ -7943,7 +8226,7 @@
           <t>Peque</t>
         </is>
       </c>
-      <c r="B24" s="32">
+      <c r="B24" s="41">
         <v>2022</v>
       </c>
       <c r="C24" t="inlineStr">
@@ -7951,7 +8234,7 @@
           <t>Caña</t>
         </is>
       </c>
-      <c r="D24" s="33">
+      <c r="D24" s="42">
         <v>3240</v>
       </c>
       <c r="E24" t="inlineStr">
@@ -7959,7 +8242,7 @@
           <t>Frijol</t>
         </is>
       </c>
-      <c r="F24" s="34">
+      <c r="F24" s="43">
         <v>137.34</v>
       </c>
     </row>
@@ -7969,7 +8252,7 @@
           <t>Uramita</t>
         </is>
       </c>
-      <c r="B25" s="32">
+      <c r="B25" s="41">
         <v>2022</v>
       </c>
       <c r="C25" t="inlineStr">
@@ -7977,7 +8260,7 @@
           <t>Caña</t>
         </is>
       </c>
-      <c r="D25" s="33">
+      <c r="D25" s="42">
         <v>29650</v>
       </c>
       <c r="E25" t="inlineStr">
@@ -7985,7 +8268,7 @@
           <t>Ahuyama</t>
         </is>
       </c>
-      <c r="F25" s="34">
+      <c r="F25" s="43">
         <v>2970</v>
       </c>
     </row>
@@ -7995,7 +8278,7 @@
           <t>Abriaquí</t>
         </is>
       </c>
-      <c r="B26" s="32">
+      <c r="B26" s="41">
         <v>2023</v>
       </c>
       <c r="C26" t="inlineStr">
@@ -8003,7 +8286,7 @@
           <t>Caña</t>
         </is>
       </c>
-      <c r="D26" s="33">
+      <c r="D26" s="42">
         <v>4425.6</v>
       </c>
       <c r="E26" t="inlineStr">
@@ -8011,7 +8294,7 @@
           <t>Tomate</t>
         </is>
       </c>
-      <c r="F26" s="34">
+      <c r="F26" s="43">
         <v>320</v>
       </c>
     </row>
@@ -8021,7 +8304,7 @@
           <t>Cañasgordas</t>
         </is>
       </c>
-      <c r="B27" s="32">
+      <c r="B27" s="41">
         <v>2023</v>
       </c>
       <c r="C27" t="inlineStr">
@@ -8029,7 +8312,7 @@
           <t>Caña</t>
         </is>
       </c>
-      <c r="D27" s="33">
+      <c r="D27" s="42">
         <v>6333.6</v>
       </c>
       <c r="E27" t="inlineStr">
@@ -8037,7 +8320,7 @@
           <t>Maíz</t>
         </is>
       </c>
-      <c r="F27" s="34">
+      <c r="F27" s="43">
         <v>271.6</v>
       </c>
     </row>
@@ -8047,7 +8330,7 @@
           <t>Dabeiba</t>
         </is>
       </c>
-      <c r="B28" s="32">
+      <c r="B28" s="41">
         <v>2023</v>
       </c>
       <c r="C28" t="inlineStr">
@@ -8055,7 +8338,7 @@
           <t>Caña</t>
         </is>
       </c>
-      <c r="D28" s="33">
+      <c r="D28" s="42">
         <v>6677</v>
       </c>
       <c r="E28" t="inlineStr">
@@ -8063,7 +8346,7 @@
           <t>Yuca</t>
         </is>
       </c>
-      <c r="F28" s="34">
+      <c r="F28" s="43">
         <v>6000</v>
       </c>
     </row>
@@ -8073,7 +8356,7 @@
           <t>Frontino</t>
         </is>
       </c>
-      <c r="B29" s="32">
+      <c r="B29" s="41">
         <v>2023</v>
       </c>
       <c r="C29" t="inlineStr">
@@ -8081,7 +8364,7 @@
           <t>Caña</t>
         </is>
       </c>
-      <c r="D29" s="33">
+      <c r="D29" s="42">
         <v>101443.47</v>
       </c>
       <c r="E29" t="inlineStr">
@@ -8089,7 +8372,7 @@
           <t>Arroz</t>
         </is>
       </c>
-      <c r="F29" s="34">
+      <c r="F29" s="43">
         <v>113.86</v>
       </c>
     </row>
@@ -8099,7 +8382,7 @@
           <t>Peque</t>
         </is>
       </c>
-      <c r="B30" s="32">
+      <c r="B30" s="41">
         <v>2023</v>
       </c>
       <c r="C30" t="inlineStr">
@@ -8107,7 +8390,7 @@
           <t>Caña</t>
         </is>
       </c>
-      <c r="D30" s="33">
+      <c r="D30" s="42">
         <v>4150</v>
       </c>
       <c r="E30" t="inlineStr">
@@ -8115,7 +8398,7 @@
           <t>Frijol</t>
         </is>
       </c>
-      <c r="F30" s="34">
+      <c r="F30" s="43">
         <v>168</v>
       </c>
     </row>
@@ -8125,7 +8408,7 @@
           <t>Uramita</t>
         </is>
       </c>
-      <c r="B31" s="32">
+      <c r="B31" s="41">
         <v>2023</v>
       </c>
       <c r="C31" t="inlineStr">
@@ -8133,7 +8416,7 @@
           <t>Caña</t>
         </is>
       </c>
-      <c r="D31" s="33">
+      <c r="D31" s="42">
         <v>30400</v>
       </c>
       <c r="E31" t="inlineStr">
@@ -8141,7 +8424,7 @@
           <t>Maíz</t>
         </is>
       </c>
-      <c r="F31" s="34">
+      <c r="F31" s="43">
         <v>3187.5</v>
       </c>
     </row>
@@ -8151,7 +8434,7 @@
           <t>Abriaquí</t>
         </is>
       </c>
-      <c r="B32" s="32">
+      <c r="B32" s="41">
         <v>2024</v>
       </c>
       <c r="C32" t="inlineStr">
@@ -8159,7 +8442,7 @@
           <t>Caña</t>
         </is>
       </c>
-      <c r="D32" s="33">
+      <c r="D32" s="42">
         <v>4201.6</v>
       </c>
       <c r="E32" t="inlineStr">
@@ -8167,7 +8450,7 @@
           <t>Tomate</t>
         </is>
       </c>
-      <c r="F32" s="34">
+      <c r="F32" s="43">
         <v>140</v>
       </c>
     </row>
@@ -8177,7 +8460,7 @@
           <t>Cañasgordas</t>
         </is>
       </c>
-      <c r="B33" s="32">
+      <c r="B33" s="41">
         <v>2024</v>
       </c>
       <c r="C33" t="inlineStr">
@@ -8185,7 +8468,7 @@
           <t>Caña</t>
         </is>
       </c>
-      <c r="D33" s="33">
+      <c r="D33" s="42">
         <v>4014</v>
       </c>
       <c r="E33" t="inlineStr">
@@ -8193,7 +8476,7 @@
           <t>Maíz</t>
         </is>
       </c>
-      <c r="F33" s="34">
+      <c r="F33" s="43">
         <v>217</v>
       </c>
     </row>
@@ -8203,7 +8486,7 @@
           <t>Dabeiba</t>
         </is>
       </c>
-      <c r="B34" s="32">
+      <c r="B34" s="41">
         <v>2024</v>
       </c>
       <c r="C34" t="inlineStr">
@@ -8211,7 +8494,7 @@
           <t>Caña</t>
         </is>
       </c>
-      <c r="D34" s="33">
+      <c r="D34" s="42">
         <v>12287</v>
       </c>
       <c r="E34" t="inlineStr">
@@ -8219,7 +8502,7 @@
           <t>Yuca</t>
         </is>
       </c>
-      <c r="F34" s="34">
+      <c r="F34" s="43">
         <v>7000</v>
       </c>
     </row>
@@ -8229,7 +8512,7 @@
           <t>Frontino</t>
         </is>
       </c>
-      <c r="B35" s="32">
+      <c r="B35" s="41">
         <v>2024</v>
       </c>
       <c r="C35" t="inlineStr">
@@ -8237,7 +8520,7 @@
           <t>Caña</t>
         </is>
       </c>
-      <c r="D35" s="33">
+      <c r="D35" s="42">
         <v>100303.47</v>
       </c>
       <c r="E35" t="inlineStr">
@@ -8245,7 +8528,7 @@
           <t>Yuca</t>
         </is>
       </c>
-      <c r="F35" s="34">
+      <c r="F35" s="43">
         <v>165</v>
       </c>
     </row>
@@ -8255,7 +8538,7 @@
           <t>Peque</t>
         </is>
       </c>
-      <c r="B36" s="32">
+      <c r="B36" s="41">
         <v>2024</v>
       </c>
       <c r="C36" t="inlineStr">
@@ -8263,7 +8546,7 @@
           <t>Caña</t>
         </is>
       </c>
-      <c r="D36" s="33">
+      <c r="D36" s="42">
         <v>4250</v>
       </c>
       <c r="E36" t="inlineStr">
@@ -8271,7 +8554,7 @@
           <t>Frijol</t>
         </is>
       </c>
-      <c r="F36" s="34">
+      <c r="F36" s="43">
         <v>334</v>
       </c>
     </row>
@@ -8281,7 +8564,7 @@
           <t>Uramita</t>
         </is>
       </c>
-      <c r="B37" s="32">
+      <c r="B37" s="41">
         <v>2024</v>
       </c>
       <c r="C37" t="inlineStr">
@@ -8289,7 +8572,7 @@
           <t>Caña</t>
         </is>
       </c>
-      <c r="D37" s="33">
+      <c r="D37" s="42">
         <v>5000</v>
       </c>
       <c r="E37" t="inlineStr">
@@ -8297,7 +8580,7 @@
           <t>Maíz</t>
         </is>
       </c>
-      <c r="F37" s="34">
+      <c r="F37" s="43">
         <v>1370</v>
       </c>
     </row>
@@ -8307,7 +8590,7 @@
           <t>Abriaquí</t>
         </is>
       </c>
-      <c r="B38" s="32">
+      <c r="B38" s="41">
         <v>2025</v>
       </c>
       <c r="C38" t="inlineStr">
@@ -8315,7 +8598,7 @@
           <t>Caña</t>
         </is>
       </c>
-      <c r="D38" s="33">
+      <c r="D38" s="42">
         <v>4201.6</v>
       </c>
       <c r="E38" t="inlineStr">
@@ -8323,7 +8606,7 @@
           <t>Tomate</t>
         </is>
       </c>
-      <c r="F38" s="34">
+      <c r="F38" s="43">
         <v>320</v>
       </c>
     </row>
@@ -8333,7 +8616,7 @@
           <t>Cañasgordas</t>
         </is>
       </c>
-      <c r="B39" s="32">
+      <c r="B39" s="41">
         <v>2025</v>
       </c>
       <c r="C39" t="inlineStr">
@@ -8341,7 +8624,7 @@
           <t>Caña</t>
         </is>
       </c>
-      <c r="D39" s="33">
+      <c r="D39" s="42">
         <v>4014</v>
       </c>
       <c r="E39" t="inlineStr">
@@ -8349,7 +8632,7 @@
           <t>Maíz</t>
         </is>
       </c>
-      <c r="F39" s="34">
+      <c r="F39" s="43">
         <v>189</v>
       </c>
     </row>
@@ -8359,7 +8642,7 @@
           <t>Dabeiba</t>
         </is>
       </c>
-      <c r="B40" s="32">
+      <c r="B40" s="41">
         <v>2025</v>
       </c>
       <c r="C40" t="inlineStr">
@@ -8367,7 +8650,7 @@
           <t>Caña</t>
         </is>
       </c>
-      <c r="D40" s="33">
+      <c r="D40" s="42">
         <v>13607</v>
       </c>
       <c r="E40" t="inlineStr">
@@ -8375,7 +8658,7 @@
           <t>Yuca</t>
         </is>
       </c>
-      <c r="F40" s="34">
+      <c r="F40" s="43">
         <v>3400</v>
       </c>
     </row>
@@ -8385,7 +8668,7 @@
           <t>Frontino</t>
         </is>
       </c>
-      <c r="B41" s="32">
+      <c r="B41" s="41">
         <v>2025</v>
       </c>
       <c r="C41" t="inlineStr">
@@ -8393,7 +8676,7 @@
           <t>Caña</t>
         </is>
       </c>
-      <c r="D41" s="33">
+      <c r="D41" s="42">
         <v>71803.47</v>
       </c>
       <c r="E41" t="inlineStr">
@@ -8401,7 +8684,7 @@
           <t>Yuca</t>
         </is>
       </c>
-      <c r="F41" s="34">
+      <c r="F41" s="43">
         <v>154</v>
       </c>
     </row>
@@ -8411,7 +8694,7 @@
           <t>Peque</t>
         </is>
       </c>
-      <c r="B42" s="32">
+      <c r="B42" s="41">
         <v>2025</v>
       </c>
       <c r="C42" t="inlineStr">
@@ -8419,7 +8702,7 @@
           <t>Caña</t>
         </is>
       </c>
-      <c r="D42" s="33">
+      <c r="D42" s="42">
         <v>5084</v>
       </c>
       <c r="E42" t="inlineStr">
@@ -8427,7 +8710,7 @@
           <t>Frijol</t>
         </is>
       </c>
-      <c r="F42" s="34">
+      <c r="F42" s="43">
         <v>172</v>
       </c>
     </row>
@@ -8437,7 +8720,7 @@
           <t>Uramita</t>
         </is>
       </c>
-      <c r="B43" s="32">
+      <c r="B43" s="41">
         <v>2025</v>
       </c>
       <c r="C43" t="inlineStr">
@@ -8445,7 +8728,7 @@
           <t>Caña</t>
         </is>
       </c>
-      <c r="D43" s="33">
+      <c r="D43" s="42">
         <v>5000</v>
       </c>
       <c r="E43" t="inlineStr">
@@ -8453,7 +8736,7 @@
           <t>Maíz</t>
         </is>
       </c>
-      <c r="F43" s="34">
+      <c r="F43" s="43">
         <v>1065</v>
       </c>
     </row>
@@ -8469,77 +8752,77 @@
   <dimension ref="A1:L50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="44.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="43.711"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="45.711"/>
-    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="60.711"/>
-    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="34.711"/>
-    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="45.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="44.711"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="46.711"/>
+    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="61.711"/>
+    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
+    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="45" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="45" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="45" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="45" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="45" t="inlineStr">
         <is>
           <t>Año</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="45" t="inlineStr">
         <is>
           <t>Producción de cultivos permanentes (t)</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="45" t="inlineStr">
         <is>
           <t>Producción de cultivos transitorios (t)</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="45" t="inlineStr">
         <is>
           <t>Producción agrícola total del municipio (t)</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="45" t="inlineStr">
         <is>
           <t>Producción agrícola total de la provincia (t)</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="45" t="inlineStr">
         <is>
           <t>Participación del municipio en la producción de la provincia</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="45" t="inlineStr">
         <is>
           <t>Proporción de cultivos permanentes</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="45" t="inlineStr">
         <is>
           <t>Proporción de cultivos transitorios</t>
         </is>
@@ -8564,28 +8847,28 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E2" s="35">
+      <c r="E2" s="47">
         <v>2019</v>
       </c>
-      <c r="F2" s="37">
+      <c r="F2" s="49">
         <v>32407.43</v>
       </c>
-      <c r="G2" s="39">
+      <c r="G2" s="51">
         <v>6139</v>
       </c>
-      <c r="H2" s="41">
+      <c r="H2" s="53">
         <v>38546.43</v>
       </c>
-      <c r="I2" s="43">
+      <c r="I2" s="55">
         <v>119675.54</v>
       </c>
-      <c r="J2" s="45">
+      <c r="J2" s="57">
         <v>0.322091130735654</v>
       </c>
-      <c r="K2" s="47">
+      <c r="K2" s="59">
         <v>0.840737520958491</v>
       </c>
-      <c r="L2" s="49">
+      <c r="L2" s="61">
         <v>0.159262479041509</v>
       </c>
     </row>
@@ -8608,28 +8891,28 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E3" s="35">
+      <c r="E3" s="47">
         <v>2019</v>
       </c>
-      <c r="F3" s="37">
+      <c r="F3" s="49">
         <v>25096.6</v>
       </c>
-      <c r="G3" s="39">
+      <c r="G3" s="51">
         <v>9809.3</v>
       </c>
-      <c r="H3" s="41">
+      <c r="H3" s="53">
         <v>34905.9</v>
       </c>
-      <c r="I3" s="43">
+      <c r="I3" s="55">
         <v>119675.54</v>
       </c>
-      <c r="J3" s="45">
+      <c r="J3" s="57">
         <v>0.291671130124</v>
       </c>
-      <c r="K3" s="47">
+      <c r="K3" s="59">
         <v>0.718978739983785</v>
       </c>
-      <c r="L3" s="49">
+      <c r="L3" s="61">
         <v>0.281021260016215</v>
       </c>
     </row>
@@ -8652,28 +8935,28 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E4" s="35">
+      <c r="E4" s="47">
         <v>2019</v>
       </c>
-      <c r="F4" s="37">
+      <c r="F4" s="49">
         <v>17454.25</v>
       </c>
-      <c r="G4" s="39">
+      <c r="G4" s="51">
         <v>514.3</v>
       </c>
-      <c r="H4" s="41">
+      <c r="H4" s="53">
         <v>17968.55</v>
       </c>
-      <c r="I4" s="43">
+      <c r="I4" s="55">
         <v>119675.54</v>
       </c>
-      <c r="J4" s="45">
+      <c r="J4" s="57">
         <v>0.150143880696089</v>
       </c>
-      <c r="K4" s="47">
+      <c r="K4" s="59">
         <v>0.971377768378639</v>
       </c>
-      <c r="L4" s="49">
+      <c r="L4" s="61">
         <v>0.0286222316213607</v>
       </c>
     </row>
@@ -8696,28 +8979,28 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E5" s="35">
+      <c r="E5" s="47">
         <v>2019</v>
       </c>
-      <c r="F5" s="37">
+      <c r="F5" s="49">
         <v>15571.85</v>
       </c>
-      <c r="G5" s="39">
+      <c r="G5" s="51">
         <v>431.93</v>
       </c>
-      <c r="H5" s="41">
+      <c r="H5" s="53">
         <v>16003.78</v>
       </c>
-      <c r="I5" s="43">
+      <c r="I5" s="55">
         <v>119675.54</v>
       </c>
-      <c r="J5" s="45">
+      <c r="J5" s="57">
         <v>0.133726407250805</v>
       </c>
-      <c r="K5" s="47">
+      <c r="K5" s="59">
         <v>0.973010751210027</v>
       </c>
-      <c r="L5" s="49">
+      <c r="L5" s="61">
         <v>0.0269892487899734</v>
       </c>
     </row>
@@ -8740,28 +9023,28 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E6" s="35">
+      <c r="E6" s="47">
         <v>2019</v>
       </c>
-      <c r="F6" s="37">
+      <c r="F6" s="49">
         <v>5781.5</v>
       </c>
-      <c r="G6" s="39">
+      <c r="G6" s="51">
         <v>915.88</v>
       </c>
-      <c r="H6" s="41">
+      <c r="H6" s="53">
         <v>6697.38</v>
       </c>
-      <c r="I6" s="43">
+      <c r="I6" s="55">
         <v>119675.54</v>
       </c>
-      <c r="J6" s="45">
+      <c r="J6" s="57">
         <v>0.0559628141222509</v>
       </c>
-      <c r="K6" s="47">
+      <c r="K6" s="59">
         <v>0.863248016388498</v>
       </c>
-      <c r="L6" s="49">
+      <c r="L6" s="61">
         <v>0.136751983611502</v>
       </c>
     </row>
@@ -8784,74 +9067,74 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E7" s="35">
+      <c r="E7" s="47">
         <v>2019</v>
       </c>
-      <c r="F7" s="37">
+      <c r="F7" s="49">
         <v>5171.5</v>
       </c>
-      <c r="G7" s="39">
+      <c r="G7" s="51">
         <v>382</v>
       </c>
-      <c r="H7" s="41">
+      <c r="H7" s="53">
         <v>5553.5</v>
       </c>
-      <c r="I7" s="43">
+      <c r="I7" s="55">
         <v>119675.54</v>
       </c>
-      <c r="J7" s="45">
+      <c r="J7" s="57">
         <v>0.046404637071201</v>
       </c>
-      <c r="K7" s="47">
+      <c r="K7" s="59">
         <v>0.931214549383272</v>
       </c>
-      <c r="L7" s="49">
+      <c r="L7" s="61">
         <v>0.0687854506167282</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="46" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="46" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="46" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="E8" s="36">
+      <c r="D8" s="46" t="inlineStr">
+        <is>
+          <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="E8" s="48">
         <v>2019</v>
       </c>
-      <c r="F8" s="38">
+      <c r="F8" s="50">
         <v>101483.13</v>
       </c>
-      <c r="G8" s="40">
+      <c r="G8" s="52">
         <v>18192.41</v>
       </c>
-      <c r="H8" s="42">
+      <c r="H8" s="54">
         <v>119675.54</v>
       </c>
-      <c r="I8" s="44">
+      <c r="I8" s="56">
         <v>119675.54</v>
       </c>
-      <c r="J8" s="46">
+      <c r="J8" s="58">
         <v>1</v>
       </c>
-      <c r="K8" s="48">
+      <c r="K8" s="60">
         <v>0.847985561627714</v>
       </c>
-      <c r="L8" s="50">
+      <c r="L8" s="62">
         <v>0.152014438372286</v>
       </c>
     </row>
@@ -8874,28 +9157,28 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E9" s="35">
+      <c r="E9" s="47">
         <v>2020</v>
       </c>
-      <c r="F9" s="37">
+      <c r="F9" s="49">
         <v>140618.57</v>
       </c>
-      <c r="G9" s="39">
+      <c r="G9" s="51">
         <v>452.75</v>
       </c>
-      <c r="H9" s="41">
+      <c r="H9" s="53">
         <v>141071.32</v>
       </c>
-      <c r="I9" s="43">
+      <c r="I9" s="55">
         <v>245460.13</v>
       </c>
-      <c r="J9" s="45">
+      <c r="J9" s="57">
         <v>0.574721931419168</v>
       </c>
-      <c r="K9" s="47">
+      <c r="K9" s="59">
         <v>0.996790630441397</v>
       </c>
-      <c r="L9" s="49">
+      <c r="L9" s="61">
         <v>0.00320936955860341</v>
       </c>
     </row>
@@ -8918,28 +9201,28 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E10" s="35">
+      <c r="E10" s="47">
         <v>2020</v>
       </c>
-      <c r="F10" s="37">
+      <c r="F10" s="49">
         <v>33034.95</v>
       </c>
-      <c r="G10" s="39">
+      <c r="G10" s="51">
         <v>8348.5</v>
       </c>
-      <c r="H10" s="41">
+      <c r="H10" s="53">
         <v>41383.45</v>
       </c>
-      <c r="I10" s="43">
+      <c r="I10" s="55">
         <v>245460.13</v>
       </c>
-      <c r="J10" s="45">
+      <c r="J10" s="57">
         <v>0.168595404883066</v>
       </c>
-      <c r="K10" s="47">
+      <c r="K10" s="59">
         <v>0.798264765262442</v>
       </c>
-      <c r="L10" s="49">
+      <c r="L10" s="61">
         <v>0.201735234737558</v>
       </c>
     </row>
@@ -8962,28 +9245,28 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E11" s="35">
+      <c r="E11" s="47">
         <v>2020</v>
       </c>
-      <c r="F11" s="37">
+      <c r="F11" s="49">
         <v>22311.16</v>
       </c>
-      <c r="G11" s="39">
+      <c r="G11" s="51">
         <v>11970.55</v>
       </c>
-      <c r="H11" s="41">
+      <c r="H11" s="53">
         <v>34281.71</v>
       </c>
-      <c r="I11" s="43">
+      <c r="I11" s="55">
         <v>245460.13</v>
       </c>
-      <c r="J11" s="45">
+      <c r="J11" s="57">
         <v>0.139663048332941</v>
       </c>
-      <c r="K11" s="47">
+      <c r="K11" s="59">
         <v>0.650818176806233</v>
       </c>
-      <c r="L11" s="49">
+      <c r="L11" s="61">
         <v>0.349181823193767</v>
       </c>
     </row>
@@ -9006,28 +9289,28 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E12" s="35">
+      <c r="E12" s="47">
         <v>2020</v>
       </c>
-      <c r="F12" s="37">
+      <c r="F12" s="49">
         <v>15840.95</v>
       </c>
-      <c r="G12" s="39">
+      <c r="G12" s="51">
         <v>505</v>
       </c>
-      <c r="H12" s="41">
+      <c r="H12" s="53">
         <v>16345.95</v>
       </c>
-      <c r="I12" s="43">
+      <c r="I12" s="55">
         <v>245460.13</v>
       </c>
-      <c r="J12" s="45">
+      <c r="J12" s="57">
         <v>0.0665930959948567</v>
       </c>
-      <c r="K12" s="47">
+      <c r="K12" s="59">
         <v>0.969105497080317</v>
       </c>
-      <c r="L12" s="49">
+      <c r="L12" s="61">
         <v>0.0308945029196835</v>
       </c>
     </row>
@@ -9050,28 +9333,28 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E13" s="35">
+      <c r="E13" s="47">
         <v>2020</v>
       </c>
-      <c r="F13" s="37">
+      <c r="F13" s="49">
         <v>6544.25</v>
       </c>
-      <c r="G13" s="39">
+      <c r="G13" s="51">
         <v>652.75</v>
       </c>
-      <c r="H13" s="41">
+      <c r="H13" s="53">
         <v>7197</v>
       </c>
-      <c r="I13" s="43">
+      <c r="I13" s="55">
         <v>245460.13</v>
       </c>
-      <c r="J13" s="45">
+      <c r="J13" s="57">
         <v>0.0293204440167126</v>
       </c>
-      <c r="K13" s="47">
+      <c r="K13" s="59">
         <v>0.909302487147423</v>
       </c>
-      <c r="L13" s="49">
+      <c r="L13" s="61">
         <v>0.0906975128525775</v>
       </c>
     </row>
@@ -9094,74 +9377,74 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E14" s="35">
+      <c r="E14" s="47">
         <v>2020</v>
       </c>
-      <c r="F14" s="37">
+      <c r="F14" s="49">
         <v>4721</v>
       </c>
-      <c r="G14" s="39">
+      <c r="G14" s="51">
         <v>459.7</v>
       </c>
-      <c r="H14" s="41">
+      <c r="H14" s="53">
         <v>5180.7</v>
       </c>
-      <c r="I14" s="43">
+      <c r="I14" s="55">
         <v>245460.13</v>
       </c>
-      <c r="J14" s="45">
+      <c r="J14" s="57">
         <v>0.0211060753532559</v>
       </c>
-      <c r="K14" s="47">
+      <c r="K14" s="59">
         <v>0.911266817225472</v>
       </c>
-      <c r="L14" s="49">
+      <c r="L14" s="61">
         <v>0.0887331827745285</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="46" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="46" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="46" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="E15" s="36">
+      <c r="D15" s="46" t="inlineStr">
+        <is>
+          <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="E15" s="48">
         <v>2020</v>
       </c>
-      <c r="F15" s="38">
+      <c r="F15" s="50">
         <v>223070.88</v>
       </c>
-      <c r="G15" s="40">
+      <c r="G15" s="52">
         <v>22389.25</v>
       </c>
-      <c r="H15" s="42">
+      <c r="H15" s="54">
         <v>245460.13</v>
       </c>
-      <c r="I15" s="44">
+      <c r="I15" s="56">
         <v>245460.13</v>
       </c>
-      <c r="J15" s="46">
+      <c r="J15" s="58">
         <v>1</v>
       </c>
-      <c r="K15" s="48">
+      <c r="K15" s="60">
         <v>0.908786612310521</v>
       </c>
-      <c r="L15" s="50">
+      <c r="L15" s="62">
         <v>0.0912133876894793</v>
       </c>
     </row>
@@ -9184,28 +9467,28 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E16" s="35">
+      <c r="E16" s="47">
         <v>2021</v>
       </c>
-      <c r="F16" s="37">
+      <c r="F16" s="49">
         <v>85494.07</v>
       </c>
-      <c r="G16" s="39">
+      <c r="G16" s="51">
         <v>485.2</v>
       </c>
-      <c r="H16" s="41">
+      <c r="H16" s="53">
         <v>85979.27</v>
       </c>
-      <c r="I16" s="43">
+      <c r="I16" s="55">
         <v>199787.05</v>
       </c>
-      <c r="J16" s="45">
+      <c r="J16" s="57">
         <v>0.430354570028438</v>
       </c>
-      <c r="K16" s="47">
+      <c r="K16" s="59">
         <v>0.994356779256209</v>
       </c>
-      <c r="L16" s="49">
+      <c r="L16" s="61">
         <v>0.00564322074379092</v>
       </c>
     </row>
@@ -9228,28 +9511,28 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E17" s="35">
+      <c r="E17" s="47">
         <v>2021</v>
       </c>
-      <c r="F17" s="37">
+      <c r="F17" s="49">
         <v>42309.61</v>
       </c>
-      <c r="G17" s="39">
+      <c r="G17" s="51">
         <v>8800.19</v>
       </c>
-      <c r="H17" s="41">
+      <c r="H17" s="53">
         <v>51109.8</v>
       </c>
-      <c r="I17" s="43">
+      <c r="I17" s="55">
         <v>199787.05</v>
       </c>
-      <c r="J17" s="45">
+      <c r="J17" s="57">
         <v>0.255821385820552</v>
       </c>
-      <c r="K17" s="47">
+      <c r="K17" s="59">
         <v>0.827817952721396</v>
       </c>
-      <c r="L17" s="49">
+      <c r="L17" s="61">
         <v>0.172182047278604</v>
       </c>
     </row>
@@ -9272,28 +9555,28 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E18" s="35">
+      <c r="E18" s="47">
         <v>2021</v>
       </c>
-      <c r="F18" s="37">
+      <c r="F18" s="49">
         <v>22246.13</v>
       </c>
-      <c r="G18" s="39">
+      <c r="G18" s="51">
         <v>7978.6</v>
       </c>
-      <c r="H18" s="41">
+      <c r="H18" s="53">
         <v>30224.73</v>
       </c>
-      <c r="I18" s="43">
+      <c r="I18" s="55">
         <v>199787.05</v>
       </c>
-      <c r="J18" s="45">
+      <c r="J18" s="57">
         <v>0.151284730416711</v>
       </c>
-      <c r="K18" s="47">
+      <c r="K18" s="59">
         <v>0.73602411005822</v>
       </c>
-      <c r="L18" s="49">
+      <c r="L18" s="61">
         <v>0.263975889941779</v>
       </c>
     </row>
@@ -9316,28 +9599,28 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E19" s="35">
+      <c r="E19" s="47">
         <v>2021</v>
       </c>
-      <c r="F19" s="37">
+      <c r="F19" s="49">
         <v>18965.68</v>
       </c>
-      <c r="G19" s="39">
+      <c r="G19" s="51">
         <v>554.5</v>
       </c>
-      <c r="H19" s="41">
+      <c r="H19" s="53">
         <v>19520.18</v>
       </c>
-      <c r="I19" s="43">
+      <c r="I19" s="55">
         <v>199787.05</v>
       </c>
-      <c r="J19" s="45">
+      <c r="J19" s="57">
         <v>0.097704931325629</v>
       </c>
-      <c r="K19" s="47">
+      <c r="K19" s="59">
         <v>0.971593499650106</v>
       </c>
-      <c r="L19" s="49">
+      <c r="L19" s="61">
         <v>0.0284065003498943</v>
       </c>
     </row>
@@ -9360,28 +9643,28 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E20" s="35">
+      <c r="E20" s="47">
         <v>2021</v>
       </c>
-      <c r="F20" s="37">
+      <c r="F20" s="49">
         <v>6895.87</v>
       </c>
-      <c r="G20" s="39">
+      <c r="G20" s="51">
         <v>893.62</v>
       </c>
-      <c r="H20" s="41">
+      <c r="H20" s="53">
         <v>7789.49</v>
       </c>
-      <c r="I20" s="43">
+      <c r="I20" s="55">
         <v>199787.05</v>
       </c>
-      <c r="J20" s="45">
+      <c r="J20" s="57">
         <v>0.0389889634988854</v>
       </c>
-      <c r="K20" s="47">
+      <c r="K20" s="59">
         <v>0.885278753808016</v>
       </c>
-      <c r="L20" s="49">
+      <c r="L20" s="61">
         <v>0.114721246191984</v>
       </c>
     </row>
@@ -9404,74 +9687,74 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E21" s="35">
+      <c r="E21" s="47">
         <v>2021</v>
       </c>
-      <c r="F21" s="37">
+      <c r="F21" s="49">
         <v>4789.08</v>
       </c>
-      <c r="G21" s="39">
+      <c r="G21" s="51">
         <v>374.5</v>
       </c>
-      <c r="H21" s="41">
+      <c r="H21" s="53">
         <v>5163.58</v>
       </c>
-      <c r="I21" s="43">
+      <c r="I21" s="55">
         <v>199787.05</v>
       </c>
-      <c r="J21" s="45">
+      <c r="J21" s="57">
         <v>0.0258454189097842</v>
       </c>
-      <c r="K21" s="47">
+      <c r="K21" s="59">
         <v>0.927472799879154</v>
       </c>
-      <c r="L21" s="49">
+      <c r="L21" s="61">
         <v>0.0725272001208464</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="46" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="46" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="46" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="E22" s="36">
+      <c r="D22" s="46" t="inlineStr">
+        <is>
+          <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="E22" s="48">
         <v>2021</v>
       </c>
-      <c r="F22" s="38">
+      <c r="F22" s="50">
         <v>180700.44</v>
       </c>
-      <c r="G22" s="40">
+      <c r="G22" s="52">
         <v>19086.61</v>
       </c>
-      <c r="H22" s="42">
+      <c r="H22" s="54">
         <v>199787.05</v>
       </c>
-      <c r="I22" s="44">
+      <c r="I22" s="56">
         <v>199787.05</v>
       </c>
-      <c r="J22" s="46">
+      <c r="J22" s="58">
         <v>1</v>
       </c>
-      <c r="K22" s="48">
+      <c r="K22" s="60">
         <v>0.904465229352953</v>
       </c>
-      <c r="L22" s="50">
+      <c r="L22" s="62">
         <v>0.0955347706470464</v>
       </c>
     </row>
@@ -9494,28 +9777,28 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E23" s="35">
+      <c r="E23" s="47">
         <v>2022</v>
       </c>
-      <c r="F23" s="37">
+      <c r="F23" s="49">
         <v>109089.02</v>
       </c>
-      <c r="G23" s="39">
+      <c r="G23" s="51">
         <v>465.25</v>
       </c>
-      <c r="H23" s="41">
+      <c r="H23" s="53">
         <v>109554.27</v>
       </c>
-      <c r="I23" s="43">
+      <c r="I23" s="55">
         <v>203605.92</v>
       </c>
-      <c r="J23" s="45">
+      <c r="J23" s="57">
         <v>0.538070160238956</v>
       </c>
-      <c r="K23" s="47">
+      <c r="K23" s="59">
         <v>0.995753246313448</v>
       </c>
-      <c r="L23" s="49">
+      <c r="L23" s="61">
         <v>0.00424675368655188</v>
       </c>
     </row>
@@ -9538,28 +9821,28 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E24" s="35">
+      <c r="E24" s="47">
         <v>2022</v>
       </c>
-      <c r="F24" s="37">
+      <c r="F24" s="49">
         <v>39000.64</v>
       </c>
-      <c r="G24" s="39">
+      <c r="G24" s="51">
         <v>5850</v>
       </c>
-      <c r="H24" s="41">
+      <c r="H24" s="53">
         <v>44850.64</v>
       </c>
-      <c r="I24" s="43">
+      <c r="I24" s="55">
         <v>203605.92</v>
       </c>
-      <c r="J24" s="45">
+      <c r="J24" s="57">
         <v>0.220281610672224</v>
       </c>
-      <c r="K24" s="47">
+      <c r="K24" s="59">
         <v>0.869567078641464</v>
       </c>
-      <c r="L24" s="49">
+      <c r="L24" s="61">
         <v>0.130432921358536</v>
       </c>
     </row>
@@ -9582,28 +9865,28 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E25" s="35">
+      <c r="E25" s="47">
         <v>2022</v>
       </c>
-      <c r="F25" s="37">
+      <c r="F25" s="49">
         <v>12204.91</v>
       </c>
-      <c r="G25" s="39">
+      <c r="G25" s="51">
         <v>7996.4</v>
       </c>
-      <c r="H25" s="41">
+      <c r="H25" s="53">
         <v>20201.31</v>
       </c>
-      <c r="I25" s="43">
+      <c r="I25" s="55">
         <v>203605.92</v>
       </c>
-      <c r="J25" s="45">
+      <c r="J25" s="57">
         <v>0.0992176946524934</v>
       </c>
-      <c r="K25" s="47">
+      <c r="K25" s="59">
         <v>0.604164284395418</v>
       </c>
-      <c r="L25" s="49">
+      <c r="L25" s="61">
         <v>0.395835715604582</v>
       </c>
     </row>
@@ -9626,28 +9909,28 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E26" s="35">
+      <c r="E26" s="47">
         <v>2022</v>
       </c>
-      <c r="F26" s="37">
+      <c r="F26" s="49">
         <v>14152.73</v>
       </c>
-      <c r="G26" s="39">
+      <c r="G26" s="51">
         <v>432.6</v>
       </c>
-      <c r="H26" s="41">
+      <c r="H26" s="53">
         <v>14585.33</v>
       </c>
-      <c r="I26" s="43">
+      <c r="I26" s="55">
         <v>203605.92</v>
       </c>
-      <c r="J26" s="45">
+      <c r="J26" s="57">
         <v>0.0716350978399842</v>
       </c>
-      <c r="K26" s="47">
+      <c r="K26" s="59">
         <v>0.97034006086938</v>
       </c>
-      <c r="L26" s="49">
+      <c r="L26" s="61">
         <v>0.0296599391306196</v>
       </c>
     </row>
@@ -9670,28 +9953,28 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E27" s="35">
+      <c r="E27" s="47">
         <v>2022</v>
       </c>
-      <c r="F27" s="37">
+      <c r="F27" s="49">
         <v>7116.94</v>
       </c>
-      <c r="G27" s="39">
+      <c r="G27" s="51">
         <v>2331.46</v>
       </c>
-      <c r="H27" s="41">
+      <c r="H27" s="53">
         <v>9448.4</v>
       </c>
-      <c r="I27" s="43">
+      <c r="I27" s="55">
         <v>203605.92</v>
       </c>
-      <c r="J27" s="45">
+      <c r="J27" s="57">
         <v>0.0464053304540457</v>
       </c>
-      <c r="K27" s="47">
+      <c r="K27" s="59">
         <v>0.753242877100885</v>
       </c>
-      <c r="L27" s="49">
+      <c r="L27" s="61">
         <v>0.246757122899115</v>
       </c>
     </row>
@@ -9714,74 +9997,74 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E28" s="35">
+      <c r="E28" s="47">
         <v>2022</v>
       </c>
-      <c r="F28" s="37">
+      <c r="F28" s="49">
         <v>4772.03</v>
       </c>
-      <c r="G28" s="39">
+      <c r="G28" s="51">
         <v>193.94</v>
       </c>
-      <c r="H28" s="41">
+      <c r="H28" s="53">
         <v>4965.97</v>
       </c>
-      <c r="I28" s="43">
+      <c r="I28" s="55">
         <v>203605.92</v>
       </c>
-      <c r="J28" s="45">
+      <c r="J28" s="57">
         <v>0.0243901061422968</v>
       </c>
-      <c r="K28" s="47">
+      <c r="K28" s="59">
         <v>0.960946199836084</v>
       </c>
-      <c r="L28" s="49">
+      <c r="L28" s="61">
         <v>0.0390538001639156</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" s="46" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="46" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C29" s="46" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="E29" s="36">
+      <c r="D29" s="46" t="inlineStr">
+        <is>
+          <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="E29" s="48">
         <v>2022</v>
       </c>
-      <c r="F29" s="38">
+      <c r="F29" s="50">
         <v>186336.27</v>
       </c>
-      <c r="G29" s="40">
+      <c r="G29" s="52">
         <v>17269.65</v>
       </c>
-      <c r="H29" s="42">
+      <c r="H29" s="54">
         <v>203605.92</v>
       </c>
-      <c r="I29" s="44">
+      <c r="I29" s="56">
         <v>203605.92</v>
       </c>
-      <c r="J29" s="46">
+      <c r="J29" s="58">
         <v>1</v>
       </c>
-      <c r="K29" s="48">
+      <c r="K29" s="60">
         <v>0.915181002595602</v>
       </c>
-      <c r="L29" s="50">
+      <c r="L29" s="62">
         <v>0.0848189974043977</v>
       </c>
     </row>
@@ -9804,28 +10087,28 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E30" s="35">
+      <c r="E30" s="47">
         <v>2023</v>
       </c>
-      <c r="F30" s="37">
+      <c r="F30" s="49">
         <v>103570.4</v>
       </c>
-      <c r="G30" s="39">
+      <c r="G30" s="51">
         <v>300.84</v>
       </c>
-      <c r="H30" s="41">
+      <c r="H30" s="53">
         <v>103871.24</v>
       </c>
-      <c r="I30" s="43">
+      <c r="I30" s="55">
         <v>201256.78</v>
       </c>
-      <c r="J30" s="45">
+      <c r="J30" s="57">
         <v>0.516112997534791</v>
       </c>
-      <c r="K30" s="47">
+      <c r="K30" s="59">
         <v>0.997103721877201</v>
       </c>
-      <c r="L30" s="49">
+      <c r="L30" s="61">
         <v>0.00289627812279896</v>
       </c>
     </row>
@@ -9848,28 +10131,28 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E31" s="35">
+      <c r="E31" s="47">
         <v>2023</v>
       </c>
-      <c r="F31" s="37">
+      <c r="F31" s="49">
         <v>41918.06</v>
       </c>
-      <c r="G31" s="39">
+      <c r="G31" s="51">
         <v>5500.5</v>
       </c>
-      <c r="H31" s="41">
+      <c r="H31" s="53">
         <v>47418.56</v>
       </c>
-      <c r="I31" s="43">
+      <c r="I31" s="55">
         <v>201256.78</v>
       </c>
-      <c r="J31" s="45">
+      <c r="J31" s="57">
         <v>0.235612236268512</v>
       </c>
-      <c r="K31" s="47">
+      <c r="K31" s="59">
         <v>0.884001116862258</v>
       </c>
-      <c r="L31" s="49">
+      <c r="L31" s="61">
         <v>0.115998883137742</v>
       </c>
     </row>
@@ -9892,28 +10175,28 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E32" s="35">
+      <c r="E32" s="47">
         <v>2023</v>
       </c>
-      <c r="F32" s="37">
+      <c r="F32" s="49">
         <v>14127.1</v>
       </c>
-      <c r="G32" s="39">
+      <c r="G32" s="51">
         <v>10902</v>
       </c>
-      <c r="H32" s="41">
+      <c r="H32" s="53">
         <v>25029.1</v>
       </c>
-      <c r="I32" s="43">
+      <c r="I32" s="55">
         <v>201256.78</v>
       </c>
-      <c r="J32" s="45">
+      <c r="J32" s="57">
         <v>0.124364009003821</v>
       </c>
-      <c r="K32" s="47">
+      <c r="K32" s="59">
         <v>0.564427006963894</v>
       </c>
-      <c r="L32" s="49">
+      <c r="L32" s="61">
         <v>0.435572993036106</v>
       </c>
     </row>
@@ -9936,28 +10219,28 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E33" s="35">
+      <c r="E33" s="47">
         <v>2023</v>
       </c>
-      <c r="F33" s="37">
+      <c r="F33" s="49">
         <v>12117.26</v>
       </c>
-      <c r="G33" s="39">
+      <c r="G33" s="51">
         <v>432.6</v>
       </c>
-      <c r="H33" s="41">
+      <c r="H33" s="53">
         <v>12549.86</v>
       </c>
-      <c r="I33" s="43">
+      <c r="I33" s="55">
         <v>201256.78</v>
       </c>
-      <c r="J33" s="45">
+      <c r="J33" s="57">
         <v>0.0623574520073311</v>
       </c>
-      <c r="K33" s="47">
+      <c r="K33" s="59">
         <v>0.965529495946568</v>
       </c>
-      <c r="L33" s="49">
+      <c r="L33" s="61">
         <v>0.0344705040534317</v>
       </c>
     </row>
@@ -9980,28 +10263,28 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E34" s="35">
+      <c r="E34" s="47">
         <v>2023</v>
       </c>
-      <c r="F34" s="37">
+      <c r="F34" s="49">
         <v>6551.69</v>
       </c>
-      <c r="G34" s="39">
+      <c r="G34" s="51">
         <v>472.35</v>
       </c>
-      <c r="H34" s="41">
+      <c r="H34" s="53">
         <v>7024.04</v>
       </c>
-      <c r="I34" s="43">
+      <c r="I34" s="55">
         <v>201256.78</v>
       </c>
-      <c r="J34" s="45">
+      <c r="J34" s="57">
         <v>0.0349008863204509</v>
       </c>
-      <c r="K34" s="47">
+      <c r="K34" s="59">
         <v>0.932752376125421</v>
       </c>
-      <c r="L34" s="49">
+      <c r="L34" s="61">
         <v>0.0672476238745793</v>
       </c>
     </row>
@@ -10024,74 +10307,74 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E35" s="35">
+      <c r="E35" s="47">
         <v>2023</v>
       </c>
-      <c r="F35" s="37">
+      <c r="F35" s="49">
         <v>5106.98</v>
       </c>
-      <c r="G35" s="39">
+      <c r="G35" s="51">
         <v>257</v>
       </c>
-      <c r="H35" s="41">
+      <c r="H35" s="53">
         <v>5363.98</v>
       </c>
-      <c r="I35" s="43">
+      <c r="I35" s="55">
         <v>201256.78</v>
       </c>
-      <c r="J35" s="45">
+      <c r="J35" s="57">
         <v>0.0266524188650936</v>
       </c>
-      <c r="K35" s="47">
+      <c r="K35" s="59">
         <v>0.952087815390811</v>
       </c>
-      <c r="L35" s="49">
+      <c r="L35" s="61">
         <v>0.0479121846091895</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
+      <c r="A36" s="46" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B36" s="46" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C36" s="46" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="E36" s="36">
+      <c r="D36" s="46" t="inlineStr">
+        <is>
+          <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="E36" s="48">
         <v>2023</v>
       </c>
-      <c r="F36" s="38">
+      <c r="F36" s="50">
         <v>183391.49</v>
       </c>
-      <c r="G36" s="40">
+      <c r="G36" s="52">
         <v>17865.29</v>
       </c>
-      <c r="H36" s="42">
+      <c r="H36" s="54">
         <v>201256.78</v>
       </c>
-      <c r="I36" s="44">
+      <c r="I36" s="56">
         <v>201256.78</v>
       </c>
-      <c r="J36" s="46">
+      <c r="J36" s="58">
         <v>1</v>
       </c>
-      <c r="K36" s="48">
+      <c r="K36" s="60">
         <v>0.911231363236558</v>
       </c>
-      <c r="L36" s="50">
+      <c r="L36" s="62">
         <v>0.0887686367634422</v>
       </c>
     </row>
@@ -10114,28 +10397,28 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E37" s="35">
+      <c r="E37" s="47">
         <v>2024</v>
       </c>
-      <c r="F37" s="37">
+      <c r="F37" s="49">
         <v>102188.69</v>
       </c>
-      <c r="G37" s="39">
+      <c r="G37" s="51">
         <v>518.98</v>
       </c>
-      <c r="H37" s="41">
+      <c r="H37" s="53">
         <v>102707.67</v>
       </c>
-      <c r="I37" s="43">
+      <c r="I37" s="55">
         <v>168041.09</v>
       </c>
-      <c r="J37" s="45">
+      <c r="J37" s="57">
         <v>0.611205687846943</v>
       </c>
-      <c r="K37" s="47">
+      <c r="K37" s="59">
         <v>0.994947018075671</v>
       </c>
-      <c r="L37" s="49">
+      <c r="L37" s="61">
         <v>0.00505298192432951</v>
       </c>
     </row>
@@ -10158,28 +10441,28 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E38" s="35">
+      <c r="E38" s="47">
         <v>2024</v>
       </c>
-      <c r="F38" s="37">
+      <c r="F38" s="49">
         <v>21022.96</v>
       </c>
-      <c r="G38" s="39">
+      <c r="G38" s="51">
         <v>10151.58</v>
       </c>
-      <c r="H38" s="41">
+      <c r="H38" s="53">
         <v>31174.54</v>
       </c>
-      <c r="I38" s="43">
+      <c r="I38" s="55">
         <v>168041.09</v>
       </c>
-      <c r="J38" s="45">
+      <c r="J38" s="57">
         <v>0.185517363640048</v>
       </c>
-      <c r="K38" s="47">
+      <c r="K38" s="59">
         <v>0.674363118108559</v>
       </c>
-      <c r="L38" s="49">
+      <c r="L38" s="61">
         <v>0.325636881891441</v>
       </c>
     </row>
@@ -10202,28 +10485,28 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E39" s="35">
+      <c r="E39" s="47">
         <v>2024</v>
       </c>
-      <c r="F39" s="37">
+      <c r="F39" s="49">
         <v>9065.95</v>
       </c>
-      <c r="G39" s="39">
+      <c r="G39" s="51">
         <v>1760</v>
       </c>
-      <c r="H39" s="41">
+      <c r="H39" s="53">
         <v>10825.95</v>
       </c>
-      <c r="I39" s="43">
+      <c r="I39" s="55">
         <v>168041.09</v>
       </c>
-      <c r="J39" s="45">
+      <c r="J39" s="57">
         <v>0.0644244214316867</v>
       </c>
-      <c r="K39" s="47">
+      <c r="K39" s="59">
         <v>0.837427662237494</v>
       </c>
-      <c r="L39" s="49">
+      <c r="L39" s="61">
         <v>0.162572337762506</v>
       </c>
     </row>
@@ -10246,28 +10529,28 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E40" s="35">
+      <c r="E40" s="47">
         <v>2024</v>
       </c>
-      <c r="F40" s="37">
+      <c r="F40" s="49">
         <v>9990.81</v>
       </c>
-      <c r="G40" s="39">
+      <c r="G40" s="51">
         <v>294</v>
       </c>
-      <c r="H40" s="41">
+      <c r="H40" s="53">
         <v>10284.81</v>
       </c>
-      <c r="I40" s="43">
+      <c r="I40" s="55">
         <v>168041.09</v>
       </c>
-      <c r="J40" s="45">
+      <c r="J40" s="57">
         <v>0.0612041376308616</v>
       </c>
-      <c r="K40" s="47">
+      <c r="K40" s="59">
         <v>0.971414153494328</v>
       </c>
-      <c r="L40" s="49">
+      <c r="L40" s="61">
         <v>0.028585846505672</v>
       </c>
     </row>
@@ -10290,28 +10573,28 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E41" s="35">
+      <c r="E41" s="47">
         <v>2024</v>
       </c>
-      <c r="F41" s="37">
+      <c r="F41" s="49">
         <v>6913.13</v>
       </c>
-      <c r="G41" s="39">
+      <c r="G41" s="51">
         <v>335.52</v>
       </c>
-      <c r="H41" s="41">
+      <c r="H41" s="53">
         <v>7248.65</v>
       </c>
-      <c r="I41" s="43">
+      <c r="I41" s="55">
         <v>168041.09</v>
       </c>
-      <c r="J41" s="45">
+      <c r="J41" s="57">
         <v>0.0431361758008116</v>
       </c>
-      <c r="K41" s="47">
+      <c r="K41" s="59">
         <v>0.953712760307092</v>
       </c>
-      <c r="L41" s="49">
+      <c r="L41" s="61">
         <v>0.0462872396929083</v>
       </c>
     </row>
@@ -10334,74 +10617,74 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E42" s="35">
+      <c r="E42" s="47">
         <v>2024</v>
       </c>
-      <c r="F42" s="37">
+      <c r="F42" s="49">
         <v>5380.48</v>
       </c>
-      <c r="G42" s="39">
+      <c r="G42" s="51">
         <v>418.99</v>
       </c>
-      <c r="H42" s="41">
+      <c r="H42" s="53">
         <v>5799.47</v>
       </c>
-      <c r="I42" s="43">
+      <c r="I42" s="55">
         <v>168041.09</v>
       </c>
-      <c r="J42" s="45">
+      <c r="J42" s="57">
         <v>0.0345122136496496</v>
       </c>
-      <c r="K42" s="47">
+      <c r="K42" s="59">
         <v>0.927753743014448</v>
       </c>
-      <c r="L42" s="49">
+      <c r="L42" s="61">
         <v>0.0722462569855521</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="A43" s="46" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B43" s="46" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C43" s="46" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="E43" s="36">
+      <c r="D43" s="46" t="inlineStr">
+        <is>
+          <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="E43" s="48">
         <v>2024</v>
       </c>
-      <c r="F43" s="38">
+      <c r="F43" s="50">
         <v>154562.02</v>
       </c>
-      <c r="G43" s="40">
+      <c r="G43" s="52">
         <v>13479.07</v>
       </c>
-      <c r="H43" s="42">
+      <c r="H43" s="54">
         <v>168041.09</v>
       </c>
-      <c r="I43" s="44">
+      <c r="I43" s="56">
         <v>168041.09</v>
       </c>
-      <c r="J43" s="46">
+      <c r="J43" s="58">
         <v>1</v>
       </c>
-      <c r="K43" s="48">
+      <c r="K43" s="60">
         <v>0.919787059224622</v>
       </c>
-      <c r="L43" s="50">
+      <c r="L43" s="62">
         <v>0.0802129407753782</v>
       </c>
     </row>
@@ -10424,28 +10707,28 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E44" s="35">
+      <c r="E44" s="47">
         <v>2025</v>
       </c>
-      <c r="F44" s="37">
+      <c r="F44" s="49">
         <v>73188.89</v>
       </c>
-      <c r="G44" s="39">
+      <c r="G44" s="51">
         <v>517.54</v>
       </c>
-      <c r="H44" s="41">
+      <c r="H44" s="53">
         <v>73706.43</v>
       </c>
-      <c r="I44" s="43">
+      <c r="I44" s="55">
         <v>136790.1</v>
       </c>
-      <c r="J44" s="45">
+      <c r="J44" s="57">
         <v>0.538828687163764</v>
       </c>
-      <c r="K44" s="47">
+      <c r="K44" s="59">
         <v>0.992978360232615</v>
       </c>
-      <c r="L44" s="49">
+      <c r="L44" s="61">
         <v>0.00702163976738529</v>
       </c>
     </row>
@@ -10468,28 +10751,28 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E45" s="35">
+      <c r="E45" s="47">
         <v>2025</v>
       </c>
-      <c r="F45" s="37">
+      <c r="F45" s="49">
         <v>22333.96</v>
       </c>
-      <c r="G45" s="39">
+      <c r="G45" s="51">
         <v>8528.61</v>
       </c>
-      <c r="H45" s="41">
+      <c r="H45" s="53">
         <v>30862.57</v>
       </c>
-      <c r="I45" s="43">
+      <c r="I45" s="55">
         <v>136790.1</v>
       </c>
-      <c r="J45" s="45">
+      <c r="J45" s="57">
         <v>0.225619909627963</v>
       </c>
-      <c r="K45" s="47">
+      <c r="K45" s="59">
         <v>0.723658463958121</v>
       </c>
-      <c r="L45" s="49">
+      <c r="L45" s="61">
         <v>0.276341536041879</v>
       </c>
     </row>
@@ -10512,28 +10795,28 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E46" s="35">
+      <c r="E46" s="47">
         <v>2025</v>
       </c>
-      <c r="F46" s="37">
+      <c r="F46" s="49">
         <v>9638.94</v>
       </c>
-      <c r="G46" s="39">
+      <c r="G46" s="51">
         <v>237.96</v>
       </c>
-      <c r="H46" s="41">
+      <c r="H46" s="53">
         <v>9876.9</v>
       </c>
-      <c r="I46" s="43">
+      <c r="I46" s="55">
         <v>136790.1</v>
       </c>
-      <c r="J46" s="45">
+      <c r="J46" s="57">
         <v>0.0722047867499183</v>
       </c>
-      <c r="K46" s="47">
+      <c r="K46" s="59">
         <v>0.97590742034444</v>
       </c>
-      <c r="L46" s="49">
+      <c r="L46" s="61">
         <v>0.0240925796555599</v>
       </c>
     </row>
@@ -10556,28 +10839,28 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E47" s="35">
+      <c r="E47" s="47">
         <v>2025</v>
       </c>
-      <c r="F47" s="37">
+      <c r="F47" s="49">
         <v>7854.48</v>
       </c>
-      <c r="G47" s="39">
+      <c r="G47" s="51">
         <v>1815</v>
       </c>
-      <c r="H47" s="41">
+      <c r="H47" s="53">
         <v>9669.48</v>
       </c>
-      <c r="I47" s="43">
+      <c r="I47" s="55">
         <v>136790.1</v>
       </c>
-      <c r="J47" s="45">
+      <c r="J47" s="57">
         <v>0.0706884489447701</v>
       </c>
-      <c r="K47" s="47">
+      <c r="K47" s="59">
         <v>0.812296007644672</v>
       </c>
-      <c r="L47" s="49">
+      <c r="L47" s="61">
         <v>0.187703992355328</v>
       </c>
     </row>
@@ -10600,28 +10883,28 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E48" s="35">
+      <c r="E48" s="47">
         <v>2025</v>
       </c>
-      <c r="F48" s="37">
+      <c r="F48" s="49">
         <v>6455.12</v>
       </c>
-      <c r="G48" s="39">
+      <c r="G48" s="51">
         <v>263.1</v>
       </c>
-      <c r="H48" s="41">
+      <c r="H48" s="53">
         <v>6718.22</v>
       </c>
-      <c r="I48" s="43">
+      <c r="I48" s="55">
         <v>136790.1</v>
       </c>
-      <c r="J48" s="45">
+      <c r="J48" s="57">
         <v>0.0491133495771989</v>
       </c>
-      <c r="K48" s="47">
+      <c r="K48" s="59">
         <v>0.960837840975735</v>
       </c>
-      <c r="L48" s="49">
+      <c r="L48" s="61">
         <v>0.0391621590242654</v>
       </c>
     </row>
@@ -10644,74 +10927,74 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E49" s="35">
+      <c r="E49" s="47">
         <v>2025</v>
       </c>
-      <c r="F49" s="37">
+      <c r="F49" s="49">
         <v>5400.93</v>
       </c>
-      <c r="G49" s="39">
+      <c r="G49" s="51">
         <v>555.57</v>
       </c>
-      <c r="H49" s="41">
+      <c r="H49" s="53">
         <v>5956.5</v>
       </c>
-      <c r="I49" s="43">
+      <c r="I49" s="55">
         <v>136790.1</v>
       </c>
-      <c r="J49" s="45">
+      <c r="J49" s="57">
         <v>0.0435448179363857</v>
       </c>
-      <c r="K49" s="47">
+      <c r="K49" s="59">
         <v>0.906728783681692</v>
       </c>
-      <c r="L49" s="49">
+      <c r="L49" s="61">
         <v>0.0932712163183077</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="inlineStr">
+      <c r="A50" s="46" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B50" s="46" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C50" s="46" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="E50" s="36">
+      <c r="D50" s="46" t="inlineStr">
+        <is>
+          <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="E50" s="48">
         <v>2025</v>
       </c>
-      <c r="F50" s="38">
+      <c r="F50" s="50">
         <v>124872.32</v>
       </c>
-      <c r="G50" s="40">
+      <c r="G50" s="52">
         <v>11917.78</v>
       </c>
-      <c r="H50" s="42">
+      <c r="H50" s="54">
         <v>136790.1</v>
       </c>
-      <c r="I50" s="44">
+      <c r="I50" s="56">
         <v>136790.1</v>
       </c>
-      <c r="J50" s="46">
+      <c r="J50" s="58">
         <v>1</v>
       </c>
-      <c r="K50" s="48">
+      <c r="K50" s="60">
         <v>0.912875420077915</v>
       </c>
-      <c r="L50" s="50">
+      <c r="L50" s="62">
         <v>0.087124579922085</v>
       </c>
     </row>
@@ -10727,53 +11010,53 @@
   <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="44.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="45.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="64" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="64" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="64" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="64" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="64" t="inlineStr">
         <is>
           <t>Año</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="64" t="inlineStr">
         <is>
           <t>Producción total (t)</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="64" t="inlineStr">
         <is>
           <t>Área cosechada total (ha)</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="64" t="inlineStr">
         <is>
           <t>Rendimiento (t/ha)</t>
         </is>
@@ -10798,16 +11081,16 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E2" s="51">
+      <c r="E2" s="66">
         <v>2019</v>
       </c>
-      <c r="F2" s="53">
+      <c r="F2" s="68">
         <v>6697.38</v>
       </c>
-      <c r="G2" s="55">
+      <c r="G2" s="70">
         <v>480</v>
       </c>
-      <c r="H2" s="57">
+      <c r="H2" s="72">
         <v>13.952875</v>
       </c>
     </row>
@@ -10830,16 +11113,16 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E3" s="51">
+      <c r="E3" s="66">
         <v>2019</v>
       </c>
-      <c r="F3" s="53">
+      <c r="F3" s="68">
         <v>38546.43</v>
       </c>
-      <c r="G3" s="55">
+      <c r="G3" s="70">
         <v>3530.5</v>
       </c>
-      <c r="H3" s="57">
+      <c r="H3" s="72">
         <v>10.9181220790256</v>
       </c>
     </row>
@@ -10862,16 +11145,16 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E4" s="51">
+      <c r="E4" s="66">
         <v>2019</v>
       </c>
-      <c r="F4" s="53">
+      <c r="F4" s="68">
         <v>34905.9</v>
       </c>
-      <c r="G4" s="55">
+      <c r="G4" s="70">
         <v>5066</v>
       </c>
-      <c r="H4" s="57">
+      <c r="H4" s="72">
         <v>6.89022897749704</v>
       </c>
     </row>
@@ -10894,16 +11177,16 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E5" s="51">
+      <c r="E5" s="66">
         <v>2019</v>
       </c>
-      <c r="F5" s="53">
+      <c r="F5" s="68">
         <v>16003.78</v>
       </c>
-      <c r="G5" s="55">
+      <c r="G5" s="70">
         <v>2463.5</v>
       </c>
-      <c r="H5" s="57">
+      <c r="H5" s="72">
         <v>6.49635883905013</v>
       </c>
     </row>
@@ -10926,16 +11209,16 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E6" s="51">
+      <c r="E6" s="66">
         <v>2019</v>
       </c>
-      <c r="F6" s="53">
+      <c r="F6" s="68">
         <v>17968.55</v>
       </c>
-      <c r="G6" s="55">
+      <c r="G6" s="70">
         <v>3224.2</v>
       </c>
-      <c r="H6" s="57">
+      <c r="H6" s="72">
         <v>5.57302586688171</v>
       </c>
     </row>
@@ -10958,50 +11241,50 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E7" s="51">
+      <c r="E7" s="66">
         <v>2019</v>
       </c>
-      <c r="F7" s="53">
+      <c r="F7" s="68">
         <v>5553.5</v>
       </c>
-      <c r="G7" s="55">
+      <c r="G7" s="70">
         <v>1776</v>
       </c>
-      <c r="H7" s="57">
+      <c r="H7" s="72">
         <v>3.12697072072072</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="65" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="65" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="65" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="E8" s="52">
+      <c r="D8" s="65" t="inlineStr">
+        <is>
+          <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="E8" s="67">
         <v>2019</v>
       </c>
-      <c r="F8" s="54">
+      <c r="F8" s="69">
         <v>119675.54</v>
       </c>
-      <c r="G8" s="56">
+      <c r="G8" s="71">
         <v>16540.2</v>
       </c>
-      <c r="H8" s="58">
+      <c r="H8" s="73">
         <v>7.23543487986844</v>
       </c>
     </row>
@@ -11024,16 +11307,16 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E9" s="51">
+      <c r="E9" s="66">
         <v>2020</v>
       </c>
-      <c r="F9" s="53">
+      <c r="F9" s="68">
         <v>141071.32</v>
       </c>
-      <c r="G9" s="55">
+      <c r="G9" s="70">
         <v>2572.44</v>
       </c>
-      <c r="H9" s="57">
+      <c r="H9" s="72">
         <v>54.8394986860724</v>
       </c>
     </row>
@@ -11056,16 +11339,16 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E10" s="51">
+      <c r="E10" s="66">
         <v>2020</v>
       </c>
-      <c r="F10" s="53">
+      <c r="F10" s="68">
         <v>7197</v>
       </c>
-      <c r="G10" s="55">
+      <c r="G10" s="70">
         <v>543.6</v>
       </c>
-      <c r="H10" s="57">
+      <c r="H10" s="72">
         <v>13.2395143487859</v>
       </c>
     </row>
@@ -11088,16 +11371,16 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E11" s="51">
+      <c r="E11" s="66">
         <v>2020</v>
       </c>
-      <c r="F11" s="53">
+      <c r="F11" s="68">
         <v>41383.45</v>
       </c>
-      <c r="G11" s="55">
+      <c r="G11" s="70">
         <v>4070.5</v>
       </c>
-      <c r="H11" s="57">
+      <c r="H11" s="72">
         <v>10.1666748556688</v>
       </c>
     </row>
@@ -11120,16 +11403,16 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E12" s="51">
+      <c r="E12" s="66">
         <v>2020</v>
       </c>
-      <c r="F12" s="53">
+      <c r="F12" s="68">
         <v>34281.71</v>
       </c>
-      <c r="G12" s="55">
+      <c r="G12" s="70">
         <v>5679.7</v>
       </c>
-      <c r="H12" s="57">
+      <c r="H12" s="72">
         <v>6.03583111784073</v>
       </c>
     </row>
@@ -11152,16 +11435,16 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E13" s="51">
+      <c r="E13" s="66">
         <v>2020</v>
       </c>
-      <c r="F13" s="53">
+      <c r="F13" s="68">
         <v>16345.95</v>
       </c>
-      <c r="G13" s="55">
+      <c r="G13" s="70">
         <v>3293.2</v>
       </c>
-      <c r="H13" s="57">
+      <c r="H13" s="72">
         <v>4.9635460949836</v>
       </c>
     </row>
@@ -11184,50 +11467,50 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E14" s="51">
+      <c r="E14" s="66">
         <v>2020</v>
       </c>
-      <c r="F14" s="53">
+      <c r="F14" s="68">
         <v>5180.7</v>
       </c>
-      <c r="G14" s="55">
+      <c r="G14" s="70">
         <v>1809</v>
       </c>
-      <c r="H14" s="57">
+      <c r="H14" s="72">
         <v>2.86384742951907</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="65" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="65" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="65" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="E15" s="52">
+      <c r="D15" s="65" t="inlineStr">
+        <is>
+          <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="E15" s="67">
         <v>2020</v>
       </c>
-      <c r="F15" s="54">
+      <c r="F15" s="69">
         <v>245460.13</v>
       </c>
-      <c r="G15" s="56">
+      <c r="G15" s="71">
         <v>17968.44</v>
       </c>
-      <c r="H15" s="58">
+      <c r="H15" s="73">
         <v>13.6606255189655</v>
       </c>
     </row>
@@ -11250,16 +11533,16 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E16" s="51">
+      <c r="E16" s="66">
         <v>2021</v>
       </c>
-      <c r="F16" s="53">
+      <c r="F16" s="68">
         <v>85979.27</v>
       </c>
-      <c r="G16" s="55">
+      <c r="G16" s="70">
         <v>2664.75</v>
       </c>
-      <c r="H16" s="57">
+      <c r="H16" s="72">
         <v>32.265417018482</v>
       </c>
     </row>
@@ -11282,16 +11565,16 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E17" s="51">
+      <c r="E17" s="66">
         <v>2021</v>
       </c>
-      <c r="F17" s="53">
+      <c r="F17" s="68">
         <v>7789.49</v>
       </c>
-      <c r="G17" s="55">
+      <c r="G17" s="70">
         <v>584.05</v>
       </c>
-      <c r="H17" s="57">
+      <c r="H17" s="72">
         <v>13.33702593956</v>
       </c>
     </row>
@@ -11314,16 +11597,16 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E18" s="51">
+      <c r="E18" s="66">
         <v>2021</v>
       </c>
-      <c r="F18" s="53">
+      <c r="F18" s="68">
         <v>51109.8</v>
       </c>
-      <c r="G18" s="55">
+      <c r="G18" s="70">
         <v>4321.61</v>
       </c>
-      <c r="H18" s="57">
+      <c r="H18" s="72">
         <v>11.8265646367905</v>
       </c>
     </row>
@@ -11346,16 +11629,16 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E19" s="51">
+      <c r="E19" s="66">
         <v>2021</v>
       </c>
-      <c r="F19" s="53">
+      <c r="F19" s="68">
         <v>19520.18</v>
       </c>
-      <c r="G19" s="55">
+      <c r="G19" s="70">
         <v>3227.49</v>
       </c>
-      <c r="H19" s="57">
+      <c r="H19" s="72">
         <v>6.04809929697691</v>
       </c>
     </row>
@@ -11378,16 +11661,16 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E20" s="51">
+      <c r="E20" s="66">
         <v>2021</v>
       </c>
-      <c r="F20" s="53">
+      <c r="F20" s="68">
         <v>30224.73</v>
       </c>
-      <c r="G20" s="55">
+      <c r="G20" s="70">
         <v>5732.92</v>
       </c>
-      <c r="H20" s="57">
+      <c r="H20" s="72">
         <v>5.27213531673214</v>
       </c>
     </row>
@@ -11410,50 +11693,50 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E21" s="51">
+      <c r="E21" s="66">
         <v>2021</v>
       </c>
-      <c r="F21" s="53">
+      <c r="F21" s="68">
         <v>5163.58</v>
       </c>
-      <c r="G21" s="55">
+      <c r="G21" s="70">
         <v>1640.55</v>
       </c>
-      <c r="H21" s="57">
+      <c r="H21" s="72">
         <v>3.14746883667063</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="65" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="65" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="65" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="E22" s="52">
+      <c r="D22" s="65" t="inlineStr">
+        <is>
+          <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="E22" s="67">
         <v>2021</v>
       </c>
-      <c r="F22" s="54">
+      <c r="F22" s="69">
         <v>199787.05</v>
       </c>
-      <c r="G22" s="56">
+      <c r="G22" s="71">
         <v>18171.37</v>
       </c>
-      <c r="H22" s="58">
+      <c r="H22" s="73">
         <v>10.9946058002231</v>
       </c>
     </row>
@@ -11476,16 +11759,16 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E23" s="51">
+      <c r="E23" s="66">
         <v>2022</v>
       </c>
-      <c r="F23" s="53">
+      <c r="F23" s="68">
         <v>109554.27</v>
       </c>
-      <c r="G23" s="55">
+      <c r="G23" s="70">
         <v>2771.3</v>
       </c>
-      <c r="H23" s="57">
+      <c r="H23" s="72">
         <v>39.5317251831271</v>
       </c>
     </row>
@@ -11508,16 +11791,16 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E24" s="51">
+      <c r="E24" s="66">
         <v>2022</v>
       </c>
-      <c r="F24" s="53">
+      <c r="F24" s="68">
         <v>44850.64</v>
       </c>
-      <c r="G24" s="55">
+      <c r="G24" s="70">
         <v>3193.02</v>
       </c>
-      <c r="H24" s="57">
+      <c r="H24" s="72">
         <v>14.0464638492712</v>
       </c>
     </row>
@@ -11540,16 +11823,16 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E25" s="51">
+      <c r="E25" s="66">
         <v>2022</v>
       </c>
-      <c r="F25" s="53">
+      <c r="F25" s="68">
         <v>9448.4</v>
       </c>
-      <c r="G25" s="55">
+      <c r="G25" s="70">
         <v>711.77</v>
       </c>
-      <c r="H25" s="57">
+      <c r="H25" s="72">
         <v>13.2745128342021</v>
       </c>
     </row>
@@ -11572,16 +11855,16 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E26" s="51">
+      <c r="E26" s="66">
         <v>2022</v>
       </c>
-      <c r="F26" s="53">
+      <c r="F26" s="68">
         <v>14585.33</v>
       </c>
-      <c r="G26" s="55">
+      <c r="G26" s="70">
         <v>3046.06</v>
       </c>
-      <c r="H26" s="57">
+      <c r="H26" s="72">
         <v>4.78826090096715</v>
       </c>
     </row>
@@ -11604,16 +11887,16 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E27" s="51">
+      <c r="E27" s="66">
         <v>2022</v>
       </c>
-      <c r="F27" s="53">
+      <c r="F27" s="68">
         <v>20201.31</v>
       </c>
-      <c r="G27" s="55">
+      <c r="G27" s="70">
         <v>4657.06</v>
       </c>
-      <c r="H27" s="57">
+      <c r="H27" s="72">
         <v>4.33778177648559</v>
       </c>
     </row>
@@ -11636,50 +11919,50 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E28" s="51">
+      <c r="E28" s="66">
         <v>2022</v>
       </c>
-      <c r="F28" s="53">
+      <c r="F28" s="68">
         <v>4965.97</v>
       </c>
-      <c r="G28" s="55">
+      <c r="G28" s="70">
         <v>1491.8</v>
       </c>
-      <c r="H28" s="57">
+      <c r="H28" s="72">
         <v>3.32884434910846</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" s="65" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="65" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C29" s="65" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="E29" s="52">
+      <c r="D29" s="65" t="inlineStr">
+        <is>
+          <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="E29" s="67">
         <v>2022</v>
       </c>
-      <c r="F29" s="54">
+      <c r="F29" s="69">
         <v>203605.92</v>
       </c>
-      <c r="G29" s="56">
+      <c r="G29" s="71">
         <v>15871.01</v>
       </c>
-      <c r="H29" s="58">
+      <c r="H29" s="73">
         <v>12.8287941347148</v>
       </c>
     </row>
@@ -11702,16 +11985,16 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E30" s="51">
+      <c r="E30" s="66">
         <v>2023</v>
       </c>
-      <c r="F30" s="53">
+      <c r="F30" s="68">
         <v>103871.24</v>
       </c>
-      <c r="G30" s="55">
+      <c r="G30" s="70">
         <v>2673.93</v>
       </c>
-      <c r="H30" s="57">
+      <c r="H30" s="72">
         <v>38.8459084568407</v>
       </c>
     </row>
@@ -11734,16 +12017,16 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E31" s="51">
+      <c r="E31" s="66">
         <v>2023</v>
       </c>
-      <c r="F31" s="53">
+      <c r="F31" s="68">
         <v>47418.56</v>
       </c>
-      <c r="G31" s="55">
+      <c r="G31" s="70">
         <v>3842.66</v>
       </c>
-      <c r="H31" s="57">
+      <c r="H31" s="72">
         <v>12.3400352880557</v>
       </c>
     </row>
@@ -11766,16 +12049,16 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E32" s="51">
+      <c r="E32" s="66">
         <v>2023</v>
       </c>
-      <c r="F32" s="53">
+      <c r="F32" s="68">
         <v>7024.04</v>
       </c>
-      <c r="G32" s="55">
+      <c r="G32" s="70">
         <v>700.82</v>
       </c>
-      <c r="H32" s="57">
+      <c r="H32" s="72">
         <v>10.0226020946891</v>
       </c>
     </row>
@@ -11798,16 +12081,16 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E33" s="51">
+      <c r="E33" s="66">
         <v>2023</v>
       </c>
-      <c r="F33" s="53">
+      <c r="F33" s="68">
         <v>25029.1</v>
       </c>
-      <c r="G33" s="55">
+      <c r="G33" s="70">
         <v>4254.83</v>
       </c>
-      <c r="H33" s="57">
+      <c r="H33" s="72">
         <v>5.8825146950642</v>
       </c>
     </row>
@@ -11830,16 +12113,16 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E34" s="51">
+      <c r="E34" s="66">
         <v>2023</v>
       </c>
-      <c r="F34" s="53">
+      <c r="F34" s="68">
         <v>12549.86</v>
       </c>
-      <c r="G34" s="55">
+      <c r="G34" s="70">
         <v>2938.45</v>
       </c>
-      <c r="H34" s="57">
+      <c r="H34" s="72">
         <v>4.27091153499294</v>
       </c>
     </row>
@@ -11862,50 +12145,50 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E35" s="51">
+      <c r="E35" s="66">
         <v>2023</v>
       </c>
-      <c r="F35" s="53">
+      <c r="F35" s="68">
         <v>5363.98</v>
       </c>
-      <c r="G35" s="55">
+      <c r="G35" s="70">
         <v>1510.3</v>
       </c>
-      <c r="H35" s="57">
+      <c r="H35" s="72">
         <v>3.55159902006224</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
+      <c r="A36" s="65" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B36" s="65" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C36" s="65" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="E36" s="52">
+      <c r="D36" s="65" t="inlineStr">
+        <is>
+          <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="E36" s="67">
         <v>2023</v>
       </c>
-      <c r="F36" s="54">
+      <c r="F36" s="69">
         <v>201256.78</v>
       </c>
-      <c r="G36" s="56">
+      <c r="G36" s="71">
         <v>15920.99</v>
       </c>
-      <c r="H36" s="58">
+      <c r="H36" s="73">
         <v>12.6409714471273</v>
       </c>
     </row>
@@ -11928,16 +12211,16 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E37" s="51">
+      <c r="E37" s="66">
         <v>2024</v>
       </c>
-      <c r="F37" s="53">
+      <c r="F37" s="68">
         <v>102707.67</v>
       </c>
-      <c r="G37" s="55">
+      <c r="G37" s="70">
         <v>2618.94</v>
       </c>
-      <c r="H37" s="57">
+      <c r="H37" s="72">
         <v>39.2172672913469</v>
       </c>
     </row>
@@ -11960,16 +12243,16 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E38" s="51">
+      <c r="E38" s="66">
         <v>2024</v>
       </c>
-      <c r="F38" s="53">
+      <c r="F38" s="68">
         <v>7248.65</v>
       </c>
-      <c r="G38" s="55">
+      <c r="G38" s="70">
         <v>837.45</v>
       </c>
-      <c r="H38" s="57">
+      <c r="H38" s="72">
         <v>8.65562123111828</v>
       </c>
     </row>
@@ -11992,16 +12275,16 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E39" s="51">
+      <c r="E39" s="66">
         <v>2024</v>
       </c>
-      <c r="F39" s="53">
+      <c r="F39" s="68">
         <v>31174.54</v>
       </c>
-      <c r="G39" s="55">
+      <c r="G39" s="70">
         <v>3895.36</v>
       </c>
-      <c r="H39" s="57">
+      <c r="H39" s="72">
         <v>8.00299330485501</v>
       </c>
     </row>
@@ -12024,16 +12307,16 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E40" s="51">
+      <c r="E40" s="66">
         <v>2024</v>
       </c>
-      <c r="F40" s="53">
+      <c r="F40" s="68">
         <v>10825.95</v>
       </c>
-      <c r="G40" s="55">
+      <c r="G40" s="70">
         <v>1418.75</v>
       </c>
-      <c r="H40" s="57">
+      <c r="H40" s="72">
         <v>7.63062555066079</v>
       </c>
     </row>
@@ -12056,16 +12339,16 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E41" s="51">
+      <c r="E41" s="66">
         <v>2024</v>
       </c>
-      <c r="F41" s="53">
+      <c r="F41" s="68">
         <v>10284.81</v>
       </c>
-      <c r="G41" s="55">
+      <c r="G41" s="70">
         <v>2665.2</v>
       </c>
-      <c r="H41" s="57">
+      <c r="H41" s="72">
         <v>3.85892615938766</v>
       </c>
     </row>
@@ -12088,50 +12371,50 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E42" s="51">
+      <c r="E42" s="66">
         <v>2024</v>
       </c>
-      <c r="F42" s="53">
+      <c r="F42" s="68">
         <v>5799.47</v>
       </c>
-      <c r="G42" s="55">
+      <c r="G42" s="70">
         <v>1708.05</v>
       </c>
-      <c r="H42" s="57">
+      <c r="H42" s="72">
         <v>3.39537484265683</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="A43" s="65" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B43" s="65" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C43" s="65" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="E43" s="52">
+      <c r="D43" s="65" t="inlineStr">
+        <is>
+          <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="E43" s="67">
         <v>2024</v>
       </c>
-      <c r="F43" s="54">
+      <c r="F43" s="69">
         <v>168041.09</v>
       </c>
-      <c r="G43" s="56">
+      <c r="G43" s="71">
         <v>13143.75</v>
       </c>
-      <c r="H43" s="58">
+      <c r="H43" s="73">
         <v>12.7848665715644</v>
       </c>
     </row>
@@ -12154,16 +12437,16 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E44" s="51">
+      <c r="E44" s="66">
         <v>2025</v>
       </c>
-      <c r="F44" s="53">
+      <c r="F44" s="68">
         <v>73706.43</v>
       </c>
-      <c r="G44" s="55">
+      <c r="G44" s="70">
         <v>2044.35</v>
       </c>
-      <c r="H44" s="57">
+      <c r="H44" s="72">
         <v>36.0537236774525</v>
       </c>
     </row>
@@ -12186,16 +12469,16 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E45" s="51">
+      <c r="E45" s="66">
         <v>2025</v>
       </c>
-      <c r="F45" s="53">
+      <c r="F45" s="68">
         <v>5956.5</v>
       </c>
-      <c r="G45" s="55">
+      <c r="G45" s="70">
         <v>633.79</v>
       </c>
-      <c r="H45" s="57">
+      <c r="H45" s="72">
         <v>9.39822338629514</v>
       </c>
     </row>
@@ -12218,16 +12501,16 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E46" s="51">
+      <c r="E46" s="66">
         <v>2025</v>
       </c>
-      <c r="F46" s="53">
+      <c r="F46" s="68">
         <v>30862.57</v>
       </c>
-      <c r="G46" s="55">
+      <c r="G46" s="70">
         <v>3599.04</v>
       </c>
-      <c r="H46" s="57">
+      <c r="H46" s="72">
         <v>8.57522283720103</v>
       </c>
     </row>
@@ -12250,16 +12533,16 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E47" s="51">
+      <c r="E47" s="66">
         <v>2025</v>
       </c>
-      <c r="F47" s="53">
+      <c r="F47" s="68">
         <v>9669.48</v>
       </c>
-      <c r="G47" s="55">
+      <c r="G47" s="70">
         <v>1261.76</v>
       </c>
-      <c r="H47" s="57">
+      <c r="H47" s="72">
         <v>7.66348592442303</v>
       </c>
     </row>
@@ -12282,16 +12565,16 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E48" s="51">
+      <c r="E48" s="66">
         <v>2025</v>
       </c>
-      <c r="F48" s="53">
+      <c r="F48" s="68">
         <v>6718.22</v>
       </c>
-      <c r="G48" s="55">
+      <c r="G48" s="70">
         <v>1583.74</v>
       </c>
-      <c r="H48" s="57">
+      <c r="H48" s="72">
         <v>4.24199679240279</v>
       </c>
     </row>
@@ -12314,50 +12597,50 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E49" s="51">
+      <c r="E49" s="66">
         <v>2025</v>
       </c>
-      <c r="F49" s="53">
+      <c r="F49" s="68">
         <v>9876.9</v>
       </c>
-      <c r="G49" s="55">
+      <c r="G49" s="70">
         <v>2381.02</v>
       </c>
-      <c r="H49" s="57">
+      <c r="H49" s="72">
         <v>4.14818019168256</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="inlineStr">
+      <c r="A50" s="65" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B50" s="65" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C50" s="65" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="E50" s="52">
+      <c r="D50" s="65" t="inlineStr">
+        <is>
+          <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="E50" s="67">
         <v>2025</v>
       </c>
-      <c r="F50" s="54">
+      <c r="F50" s="69">
         <v>136790.1</v>
       </c>
-      <c r="G50" s="56">
+      <c r="G50" s="71">
         <v>11503.7</v>
       </c>
-      <c r="H50" s="58">
+      <c r="H50" s="73">
         <v>11.8909655154429</v>
       </c>
     </row>
@@ -12373,29 +12656,29 @@
   <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="75" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="75" t="inlineStr">
         <is>
           <t>anio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="75" t="inlineStr">
         <is>
           <t>total_especies</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="75" t="inlineStr">
         <is>
           <t>participacion_pecuario_prov_pct</t>
         </is>
@@ -12509,23 +12792,23 @@
   <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="6.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="77" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="77" t="inlineStr">
         <is>
           <t>serie</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="77" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
